--- a/docs/최종 문서/e-학습터 개발 명세서.xlsx
+++ b/docs/최종 문서/e-학습터 개발 명세서.xlsx
@@ -2,12 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="R82c2751d2cd048c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="R2b4a20f05d4f41c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="R11b12fea921e43ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="Rf3c1caa0be96493e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="R645fd72a6111493f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="R4162ccd8fb4442b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="R3674d21be1254499"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="R5aaed758cd9f436f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="Reb41901e0b5d4aa3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="R3b2dd22a58884361"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="R2ce7ec4799074d41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="R3f42f673073a48ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="R72b247f0e6fa4144"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -82,8 +83,13 @@
       <x:b/>
       <x:color rgb="FFFFFFFF"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="15">
+  <x:fills count="17">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -155,6 +161,16 @@
         <x:fgColor rgb="FF0891B2"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E79"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="5">
     <x:border/>
@@ -219,7 +235,7 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="38">
+  <x:cellXfs count="45">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -305,6 +321,19 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="14" borderId="4" xfId="0" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -1258,10 +1287,8 @@
           <x:t xml:space="preserve">OAuthController.java</x:t>
         </x:is>
       </x:c>
-      <x:c r="E14" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GET /oauth/{provider}, /oauth/{provider}/callback, /settings/social/{provider}/connect/callback 처리. browser redirect route가 canonical</x:t>
-        </x:is>
+      <x:c r="E14" s="4" t="str">
+        <x:v>GET /oauth/{provider}, /oauth/{provider}/callback 처리. Google/GitHub OAuth browser redirect route가 canonical</x:v>
       </x:c>
       <x:c r="F14" s="4" t="inlineStr">
         <x:is>
@@ -1374,10 +1401,8 @@
           <x:t xml:space="preserve">LoginForm.java / SignupForm.java / UserSessionResponse.java</x:t>
         </x:is>
       </x:c>
-      <x:c r="E16" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MVC Form DTO와 REST response DTO 분리. email/password/nickname Bean Validation 적용</x:t>
-        </x:is>
+      <x:c r="E16" s="4" t="str">
+        <x:v>MVC Form DTO와 REST response DTO 분리. email/password/nickname Bean Validation 적용. 이메일 가입은 인증 완료 후 user_credentials.login_email로 식별</x:v>
       </x:c>
       <x:c r="F16" s="4" t="inlineStr">
         <x:is>
@@ -1432,10 +1457,8 @@
           <x:t xml:space="preserve">UserMapper.java / UserCredentialMapper.java / SocialAccountMapper.java</x:t>
         </x:is>
       </x:c>
-      <x:c r="E17" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">users, user_credentials, social_accounts CRUD와 중복 email/nickname/provider 검증</x:t>
-        </x:is>
+      <x:c r="E17" s="4" t="str">
+        <x:v>users, user_credentials, social_accounts CRUD. users.email은 중복 허용 연락처이며 login_email/nickname/provider 식별 검증은 인증 수단별로 분리</x:v>
       </x:c>
       <x:c r="F17" s="4" t="inlineStr">
         <x:is>
@@ -4874,10 +4897,8 @@
           <x:t xml:space="preserve">/api/auth/signup</x:t>
         </x:is>
       </x:c>
-      <x:c r="D2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AUTH-001. 회원가입. users, user_credentials, user_settings, user_learning_profiles transaction</x:t>
-        </x:is>
+      <x:c r="D2" s="2" t="str">
+        <x:v>AUTH-001. 이메일 회원가입. 이메일 인증 완료 후 users, user_credentials(login_email), user_settings, user_learning_profiles transaction</x:v>
       </x:c>
       <x:c r="E2" s="2" t="inlineStr">
         <x:is>
@@ -4904,10 +4925,8 @@
           <x:t xml:space="preserve">REST API v1.6 Error / Rule 참조</x:t>
         </x:is>
       </x:c>
-      <x:c r="J2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">회원가입. users, user_credentials, user_settings, user_learning_profiles transaction</x:t>
-        </x:is>
+      <x:c r="J2" s="2" t="str">
+        <x:v>이메일 회원가입. 인증 완료 이메일은 user_credentials.login_email에 UNIQUE로 저장하고 users.email은 중복 허용 연락처로 저장</x:v>
       </x:c>
       <x:c r="K2" s="2" t="inlineStr">
         <x:is>
@@ -4932,10 +4951,8 @@
           <x:t xml:space="preserve">/api/auth/login</x:t>
         </x:is>
       </x:c>
-      <x:c r="D3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AUTH-002. email/password 공통 로그인, session 생성, role별 redirect 기준 제공</x:t>
-        </x:is>
+      <x:c r="D3" s="2" t="str">
+        <x:v>AUTH-002. login_email/password 로그인, session 생성, role별 redirect 기준 제공</x:v>
       </x:c>
       <x:c r="E3" s="2" t="inlineStr">
         <x:is>
@@ -4962,10 +4979,8 @@
           <x:t xml:space="preserve">REST API v1.6 Error / Rule 참조</x:t>
         </x:is>
       </x:c>
-      <x:c r="J3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">email/password 공통 로그인, session 생성, ROLE_USER는 학습 메인, ROLE_ADMIN은 관리자 메인으로 이동</x:t>
-        </x:is>
+      <x:c r="J3" s="2" t="str">
+        <x:v>login_email/password 로그인, session 생성, ROLE_USER는 학습 메인, ROLE_ADMIN은 관리자 메인으로 이동</x:v>
       </x:c>
       <x:c r="K3" s="2" t="inlineStr">
         <x:is>
@@ -5164,10 +5179,8 @@
           <x:t xml:space="preserve">/oauth/{provider}/callback</x:t>
         </x:is>
       </x:c>
-      <x:c r="D7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AUTH-006. OAuth callback. users/social_accounts/settings/profile transaction</x:t>
-        </x:is>
+      <x:c r="D7" s="2" t="str">
+        <x:v>AUTH-006. OAuth callback. provider + provider_user_id 조회 후 미존재 시 새 users/social_accounts/settings/profile transaction</x:v>
       </x:c>
       <x:c r="E7" s="2" t="inlineStr">
         <x:is>
@@ -5194,10 +5207,8 @@
           <x:t xml:space="preserve">REST API v1.6 Error / Rule 참조</x:t>
         </x:is>
       </x:c>
-      <x:c r="J7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">OAuth callback. users/social_accounts/settings/profile transaction</x:t>
-        </x:is>
+      <x:c r="J7" s="2" t="str">
+        <x:v>Google/GitHub OAuth callback. provider 이메일이 기존 회원 이메일과 같아도 기존 계정에 연동하지 않고 새 계정 생성</x:v>
       </x:c>
       <x:c r="K7" s="2" t="inlineStr">
         <x:is>
@@ -5222,10 +5233,8 @@
           <x:t xml:space="preserve">/api/auth/social-accounts</x:t>
         </x:is>
       </x:c>
-      <x:c r="D8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AUTH-007. 연결된 social account 목록 조회</x:t>
-        </x:is>
+      <x:c r="D8" s="2" t="str">
+        <x:v>AUTH-007. 현재 계정의 social account 목록 조회</x:v>
       </x:c>
       <x:c r="E8" s="2" t="inlineStr">
         <x:is>
@@ -5338,10 +5347,8 @@
           <x:t xml:space="preserve">/settings/social/{provider}/connect, /settings/social/{provider}/callback</x:t>
         </x:is>
       </x:c>
-      <x:c r="D10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AUTH-009. 설정 화면 social connect/callback. MVC route</x:t>
-        </x:is>
+      <x:c r="D10" s="2" t="str">
+        <x:v>AUTH-009. 설정 화면 social account 연결 route. 기본 정책은 소셜 가입 계정 독립 생성이며 기존 계정 자동 병합 금지</x:v>
       </x:c>
       <x:c r="E10" s="2" t="inlineStr">
         <x:is>
@@ -9328,48 +9335,34 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="15" customHeight="1">
-      <x:c r="A8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">공통</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">검증 기준</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">반영 완료</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Notion 최신: SRS v0.6, 요구사항 v1.7, DB v1.4, REST API v1.6, MVC v1.6, 매핑표 v0.9, 구현 변경 기록 2026.07.05</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A8" s="2" t="str">
+        <x:v>공통</x:v>
+      </x:c>
+      <x:c r="B8" s="2" t="str">
+        <x:v>검증 기준</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="str">
+        <x:v>반영 완료</x:v>
+      </x:c>
+      <x:c r="D8" s="2" t="str">
+        <x:v>최신 기준: DB v1.8, 인증 수단별 독립 계정 정책, provider google/github 소문자 통일</x:v>
+      </x:c>
+      <x:c r="E8"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">공통</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">최신 기준</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">반영 완료</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D9" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SRS v0.6, 요구사항 v1.7, DB v1.4, REST API v1.6, MVC v1.6, 매핑표 v0.9, 구현 변경 기록 2026.07.05</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A9" s="12" t="str">
+        <x:v>공통</x:v>
+      </x:c>
+      <x:c r="B9" s="12" t="str">
+        <x:v>최신 기준</x:v>
+      </x:c>
+      <x:c r="C9" s="12" t="str">
+        <x:v>반영 완료</x:v>
+      </x:c>
+      <x:c r="D9" s="12" t="str">
+        <x:v>DB v1.8: users.email UNIQUE 제거, user_credentials.login_email 추가, social_accounts provider_email_verified 추가</x:v>
+      </x:c>
+      <x:c r="E9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="10" t="inlineStr">
@@ -10406,4 +10399,255 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="93.66999816894531" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="29.670000076293945" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="42" t="str">
+        <x:v>개발 명세서 최신화 요약</x:v>
+      </x:c>
+      <x:c r="B1" s="42"/>
+      <x:c r="C1" s="42"/>
+      <x:c r="D1" s="42"/>
+      <x:c r="E1" s="42"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="43" t="str">
+        <x:v>작성자: 이현겸 / 기준일: 2026-07-09</x:v>
+      </x:c>
+      <x:c r="B2" s="43" t="str">
+        <x:v>DB 명세 v1.8</x:v>
+      </x:c>
+      <x:c r="C2" s="43" t="str">
+        <x:v>인증 수단별 독립 계정 정책</x:v>
+      </x:c>
+      <x:c r="D2" s="43" t="str">
+        <x:v>DDL/sample data 수정</x:v>
+      </x:c>
+      <x:c r="E2" s="43"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="43"/>
+      <x:c r="B3" s="43"/>
+      <x:c r="C3" s="43"/>
+      <x:c r="D3" s="43"/>
+      <x:c r="E3" s="43"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="44" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B4" s="44" t="str">
+        <x:v>최신 기준</x:v>
+      </x:c>
+      <x:c r="C4" s="44" t="str">
+        <x:v>반영 내용</x:v>
+      </x:c>
+      <x:c r="D4" s="44" t="str">
+        <x:v>검증 근거</x:v>
+      </x:c>
+      <x:c r="E4" s="44" t="str">
+        <x:v>비고</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="43" t="str">
+        <x:v>변경 성격</x:v>
+      </x:c>
+      <x:c r="B5" s="43" t="str">
+        <x:v>DB/Auth 정책 변경</x:v>
+      </x:c>
+      <x:c r="C5" s="43" t="str">
+        <x:v>이메일 가입, Google 가입, GitHub 가입을 같은 이메일이어도 별도 users 계정으로 생성하는 정책 확정</x:v>
+      </x:c>
+      <x:c r="D5" s="43" t="str">
+        <x:v>사용자 확정 요청, DDL/ERD/샘플데이터 대조</x:v>
+      </x:c>
+      <x:c r="E5" s="43" t="str">
+        <x:v>자동 병합/자동 연동 제거 전제</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="43" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="B6" s="43" t="str">
+        <x:v>email 중복 허용</x:v>
+      </x:c>
+      <x:c r="C6" s="43" t="str">
+        <x:v>users.email UNIQUE 제거. email은 로그인 식별자가 아니라 연락처/표시 정보로 사용</x:v>
+      </x:c>
+      <x:c r="D6" s="43" t="str">
+        <x:v>Knowva_DDL.sql, ERD</x:v>
+      </x:c>
+      <x:c r="E6" s="43" t="str">
+        <x:v>nickname UNIQUE는 유지</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="43" t="str">
+        <x:v>user_credentials</x:v>
+      </x:c>
+      <x:c r="B7" s="43" t="str">
+        <x:v>이메일 로그인 식별자 분리</x:v>
+      </x:c>
+      <x:c r="C7" s="43" t="str">
+        <x:v>login_email UNIQUE와 email_verified_at 추가. 이메일 가입은 인증 완료 후 credential 생성</x:v>
+      </x:c>
+      <x:c r="D7" s="43" t="str">
+        <x:v>Knowva_DDL.sql, 개발명세서(API)</x:v>
+      </x:c>
+      <x:c r="E7" s="43" t="str">
+        <x:v>비밀번호 로그인은 login_email 기준</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="43" t="str">
+        <x:v>social_accounts</x:v>
+      </x:c>
+      <x:c r="B8" s="43" t="str">
+        <x:v>provider identity 기준</x:v>
+      </x:c>
+      <x:c r="C8" s="43" t="str">
+        <x:v>provider + provider_user_id를 소셜 로그인 식별자로 사용하고 provider_email은 중복 허용</x:v>
+      </x:c>
+      <x:c r="D8" s="43" t="str">
+        <x:v>Knowva_DDL.sql, ERD</x:v>
+      </x:c>
+      <x:c r="E8" s="43" t="str">
+        <x:v>provider는 google/github 소문자</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="43" t="str">
+        <x:v>social_accounts</x:v>
+      </x:c>
+      <x:c r="B9" s="43" t="str">
+        <x:v>provider 이메일 인증 상태</x:v>
+      </x:c>
+      <x:c r="C9" s="43" t="str">
+        <x:v>provider_email_verified 추가. Google email_verified와 GitHub verified 값을 저장할 수 있도록 명세화</x:v>
+      </x:c>
+      <x:c r="D9" s="43" t="str">
+        <x:v>OAuthService userinfo 흐름, DDL</x:v>
+      </x:c>
+      <x:c r="E9" s="43" t="str">
+        <x:v>소셜 이메일은 계정 병합 기준 아님</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="43" t="str">
+        <x:v>샘플데이터</x:v>
+      </x:c>
+      <x:c r="B10" s="43" t="str">
+        <x:v>중복 이메일 독립 계정 예시</x:v>
+      </x:c>
+      <x:c r="C10" s="43" t="str">
+        <x:v>learner@knowva.local 이메일 계정과 동일 이메일을 가진 google/github 소셜 계정을 별도 user_id로 추가</x:v>
+      </x:c>
+      <x:c r="D10" s="43" t="str">
+        <x:v>Knowva_sample_data.sql</x:v>
+      </x:c>
+      <x:c r="E10" s="43" t="str">
+        <x:v>소셜 샘플 계정은 password credential 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="43" t="str">
+        <x:v>로그인 흐름</x:v>
+      </x:c>
+      <x:c r="B11" s="43" t="str">
+        <x:v>자동 병합 금지</x:v>
+      </x:c>
+      <x:c r="C11" s="43" t="str">
+        <x:v>OAuth callback에서 같은 provider_user_id가 없으면 신규 users/social_accounts 생성. 같은 이메일 기존 회원 pending link 방식 제거 예정</x:v>
+      </x:c>
+      <x:c r="D11" s="43" t="str">
+        <x:v>개발명세서(API)</x:v>
+      </x:c>
+      <x:c r="E11" s="43" t="str">
+        <x:v>구현 후속 작업 필요</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="43" t="str">
+        <x:v>마이페이지/설정</x:v>
+      </x:c>
+      <x:c r="B12" s="43" t="str">
+        <x:v>계정별 독립 데이터</x:v>
+      </x:c>
+      <x:c r="C12" s="43" t="str">
+        <x:v>같은 이메일이어도 학습 진행, 결제, 프로필, 분석 데이터는 user_id별 분리</x:v>
+      </x:c>
+      <x:c r="D12" s="43" t="str">
+        <x:v>DB 정책</x:v>
+      </x:c>
+      <x:c r="E12" s="43" t="str">
+        <x:v>사용자 안내 문구 필요</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="43" t="str">
+        <x:v>ERD</x:v>
+      </x:c>
+      <x:c r="B13" s="43" t="str">
+        <x:v>DB v1.8</x:v>
+      </x:c>
+      <x:c r="C13" s="43" t="str">
+        <x:v>ERD HTML의 users/user_credentials/social_accounts 컬럼과 변경 요약 갱신</x:v>
+      </x:c>
+      <x:c r="D13" s="43" t="str">
+        <x:v>e-학습터 ERD.html</x:v>
+      </x:c>
+      <x:c r="E13" s="43" t="str">
+        <x:v>PDF는 HTML 기준 재생성</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="43" t="str">
+        <x:v>검증</x:v>
+      </x:c>
+      <x:c r="B14" s="43" t="str">
+        <x:v>문서/SQL 정합성</x:v>
+      </x:c>
+      <x:c r="C14" s="43" t="str">
+        <x:v>uk_users_email 제거, login_email/provider_email_verified 추가, provider 대소문자 통일 검색 검증</x:v>
+      </x:c>
+      <x:c r="D14" s="43" t="str">
+        <x:v>rg/mysql dry load</x:v>
+      </x:c>
+      <x:c r="E14" s="43" t="str">
+        <x:v>실서비스 구현은 다음 단계</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="43" t="str">
+        <x:v>다음 액션</x:v>
+      </x:c>
+      <x:c r="B15" s="43" t="str">
+        <x:v>로그인/마이페이지 구현</x:v>
+      </x:c>
+      <x:c r="C15" s="43" t="str">
+        <x:v>AuthService/OAuthService/SocialAccountMapper/SettingsService/templates 수정 필요</x:v>
+      </x:c>
+      <x:c r="D15" s="43" t="str">
+        <x:v>후속 요청</x:v>
+      </x:c>
+      <x:c r="E15" s="43" t="str">
+        <x:v>DB 선반영 완료 후 진행</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/docs/최종 문서/e-학습터 개발 명세서.xlsx
+++ b/docs/최종 문서/e-학습터 개발 명세서.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="R3674d21be1254499"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="R5aaed758cd9f436f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="Reb41901e0b5d4aa3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="R3b2dd22a58884361"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="R2ce7ec4799074d41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="R3f42f673073a48ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="R72b247f0e6fa4144"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="R9c48fd2d711044cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="R2237ed99d6974a6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="R37b4882d479945b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="R7b1c39e7c416435d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="R0d697a3c17c74cdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="Rd49c1a84ce364f44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="R2ede08e03c964f25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="Ra2ad5c9c34ba444b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +20,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="14">
+  <x:fonts count="17">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -88,8 +89,25 @@
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FF1F1F1F"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF404040"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F1F1F"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="17">
+  <x:fills count="20">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -171,8 +189,23 @@
         <x:fgColor rgb="FF1F4E79"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F8FC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="5">
+  <x:borders count="6">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -230,12 +263,26 @@
         <x:color rgb="FF334155"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="60">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -334,6 +381,51 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -10650,4 +10742,260 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="56" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="31" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="48" t="str">
+        <x:v>개발 명세서 최신화 요약</x:v>
+      </x:c>
+      <x:c r="B1" s="43"/>
+      <x:c r="C1" s="43"/>
+      <x:c r="D1" s="43"/>
+      <x:c r="E1" s="43"/>
+    </x:row>
+    <x:row r="2" ht="32" customHeight="1">
+      <x:c r="A2" s="51" t="str">
+        <x:v>작성자: 이현겸 / 기준일: 2026-07-11</x:v>
+      </x:c>
+      <x:c r="B2" s="51" t="str">
+        <x:v>DB 명세 v1.9</x:v>
+      </x:c>
+      <x:c r="C2" s="51" t="str">
+        <x:v>REST API v2.0</x:v>
+      </x:c>
+      <x:c r="D2" s="51" t="str">
+        <x:v>MVC v2.0</x:v>
+      </x:c>
+      <x:c r="E2" s="51" t="str">
+        <x:v>화면 매핑 v0.13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="43"/>
+      <x:c r="B3" s="43"/>
+      <x:c r="C3" s="43"/>
+      <x:c r="D3" s="43"/>
+      <x:c r="E3" s="43"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="58" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B4" s="58" t="str">
+        <x:v>최신 기준</x:v>
+      </x:c>
+      <x:c r="C4" s="58" t="str">
+        <x:v>반영 내용</x:v>
+      </x:c>
+      <x:c r="D4" s="58" t="str">
+        <x:v>검증 근거</x:v>
+      </x:c>
+      <x:c r="E4" s="58" t="str">
+        <x:v>비고</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="48" customHeight="1">
+      <x:c r="A5" s="59" t="str">
+        <x:v>변경 성격</x:v>
+      </x:c>
+      <x:c r="B5" s="59" t="str">
+        <x:v>구현 정합성·통합</x:v>
+      </x:c>
+      <x:c r="C5" s="59" t="str">
+        <x:v>7/9~7/11 병합 구현을 요구사항 정책 변경 없이 실제 controller/service/mapper·화면 기준으로 명세와 추적표에 연결</x:v>
+      </x:c>
+      <x:c r="D5" s="59" t="str">
+        <x:v>local git log, Notion 재조회</x:v>
+      </x:c>
+      <x:c r="E5" s="59" t="str">
+        <x:v>MVP 통합 검증 단계</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="48" customHeight="1">
+      <x:c r="A6" s="59" t="str">
+        <x:v>웰컴/인증</x:v>
+      </x:c>
+      <x:c r="B6" s="59" t="str">
+        <x:v>인증수단별 독립 계정</x:v>
+      </x:c>
+      <x:c r="C6" s="59" t="str">
+        <x:v>서버 주도 TutorialStepView 렌더, 로그인 UI 보강, 세션 폐기·소셜 재연결 충돌 처리</x:v>
+      </x:c>
+      <x:c r="D6" s="59" t="str">
+        <x:v>WelcomeController, AuthService, OAuthService</x:v>
+      </x:c>
+      <x:c r="E6" s="59" t="str">
+        <x:v>동일 email 자동 병합 금지</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="48" customHeight="1">
+      <x:c r="A7" s="59" t="str">
+        <x:v>학습/북마크</x:v>
+      </x:c>
+      <x:c r="B7" s="59" t="str">
+        <x:v>레슨 진행·로드맵 완료</x:v>
+      </x:c>
+      <x:c r="C7" s="59" t="str">
+        <x:v>행성 15종/스토리 카드, 레슨 완료 판정, 북마크 이론 화면과 로드맵 표시 보강</x:v>
+      </x:c>
+      <x:c r="D7" s="59" t="str">
+        <x:v>LearningController, CurriculumController, ProgressService</x:v>
+      </x:c>
+      <x:c r="E7" s="59" t="str">
+        <x:v>user_lesson_progress 집계 유지</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="48" customHeight="1">
+      <x:c r="A8" s="59" t="str">
+        <x:v>문제풀이/랭킹</x:v>
+      </x:c>
+      <x:c r="B8" s="59" t="str">
+        <x:v>레슨별 문제·오답 복습</x:v>
+      </x:c>
+      <x:c r="C8" s="59" t="str">
+        <x:v>문제풀이 완료 분기·예외 처리, 오답 재시도/복습 완료, 랭킹 조회/화면 정리</x:v>
+      </x:c>
+      <x:c r="D8" s="59" t="str">
+        <x:v>Practice/Review/Ranking controller·service·mapper</x:v>
+      </x:c>
+      <x:c r="E8" s="59" t="str">
+        <x:v>사용자 흐름 smoke test 필요</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="48" customHeight="1">
+      <x:c r="A9" s="59" t="str">
+        <x:v>커뮤니티/콘텐츠</x:v>
+      </x:c>
+      <x:c r="B9" s="59" t="str">
+        <x:v>과목 선택 홈·조회수</x:v>
+      </x:c>
+      <x:c r="C9" s="59" t="str">
+        <x:v>선택 과목 기반 커뮤니티 홈·게시글 목록/추천 콘텐츠 화면을 정리하고 community_posts.view_count 계약을 v1.9로 동기화</x:v>
+      </x:c>
+      <x:c r="D9" s="59" t="str">
+        <x:v>Community/Post/Content controller, DDL, ERD</x:v>
+      </x:c>
+      <x:c r="E9" s="59" t="str">
+        <x:v>DB/화면 정합성 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="48" customHeight="1">
+      <x:c r="A10" s="59" t="str">
+        <x:v>결제/마이페이지</x:v>
+      </x:c>
+      <x:c r="B10" s="59" t="str">
+        <x:v>카카오페이 단건 결제</x:v>
+      </x:c>
+      <x:c r="C10" s="59" t="str">
+        <x:v>결제 준비·승인·완료/실패/취소 browser flow와 학습·커뮤니티 활동 요약을 실제 화면에 연결</x:v>
+      </x:c>
+      <x:c r="D10" s="59" t="str">
+        <x:v>PaymentController, KakaoPayService, UserActivityService</x:v>
+      </x:c>
+      <x:c r="E10" s="59" t="str">
+        <x:v>외부 결제 설정은 환경변수 분리</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="48" customHeight="1">
+      <x:c r="A11" s="59" t="str">
+        <x:v>관리자</x:v>
+      </x:c>
+      <x:c r="B11" s="59" t="str">
+        <x:v>목록·필터·상태 변경</x:v>
+      </x:c>
+      <x:c r="C11" s="59" t="str">
+        <x:v>관리자 API와 페이지네이션, 통계/목록 필터, 예외 안내를 controller/service/mapper 기준으로 정리</x:v>
+      </x:c>
+      <x:c r="D11" s="59" t="str">
+        <x:v>AdminApiController, admin templates</x:v>
+      </x:c>
+      <x:c r="E11" s="59" t="str">
+        <x:v>운영 화면 통합 검증 필요</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="48" customHeight="1">
+      <x:c r="A12" s="59" t="str">
+        <x:v>Notion 문서</x:v>
+      </x:c>
+      <x:c r="B12" s="59" t="str">
+        <x:v>REST v2.0 / MVC v2.0</x:v>
+      </x:c>
+      <x:c r="C12" s="59" t="str">
+        <x:v>REST API, MVC, 화면별 기능/데이터 매핑표 v0.13, 추적표 v1.5, 구현 변경 기록 및 확장 기능 범위를 최신화</x:v>
+      </x:c>
+      <x:c r="D12" s="59" t="str">
+        <x:v>Notion fetch/update</x:v>
+      </x:c>
+      <x:c r="E12" s="59" t="str">
+        <x:v>7/9·7/10 일지와 연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="48" customHeight="1">
+      <x:c r="A13" s="59" t="str">
+        <x:v>DB/로컬 산출물</x:v>
+      </x:c>
+      <x:c r="B13" s="59" t="str">
+        <x:v>DB v1.9</x:v>
+      </x:c>
+      <x:c r="C13" s="59" t="str">
+        <x:v>DDL·샘플데이터·ERD HTML/PDF와 인증 로그인 수정 가이드를 현재 schema/seed 실행 기준으로 확인</x:v>
+      </x:c>
+      <x:c r="D13" s="59" t="str">
+        <x:v>DDL header, ERD HTML, git commit e151521</x:v>
+      </x:c>
+      <x:c r="E13" s="59" t="str">
+        <x:v>추가 schema 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="48" customHeight="1">
+      <x:c r="A14" s="59" t="str">
+        <x:v>검증</x:v>
+      </x:c>
+      <x:c r="B14" s="59" t="str">
+        <x:v>문서·코드 정합성</x:v>
+      </x:c>
+      <x:c r="C14" s="59" t="str">
+        <x:v>Notion 재조회, local git history, DDL/ERD 헤더, Gradle test 및 주요 화면 smoke test를 기준으로 후속 검증</x:v>
+      </x:c>
+      <x:c r="D14" s="59" t="str">
+        <x:v>git log, Notion fetch, local artifacts</x:v>
+      </x:c>
+      <x:c r="E14" s="59" t="str">
+        <x:v>GitHub CLI 직접 조회 불가</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="48" customHeight="1">
+      <x:c r="A15" s="59" t="str">
+        <x:v>다음 액션</x:v>
+      </x:c>
+      <x:c r="B15" s="59" t="str">
+        <x:v>통합 smoke test</x:v>
+      </x:c>
+      <x:c r="C15" s="59" t="str">
+        <x:v>로그인/웰컴, 학습/문제풀이/오답/랭킹, 커뮤니티/추천 콘텐츠, 관리자, 카카오페이 callback을 end-to-end로 점검</x:v>
+      </x:c>
+      <x:c r="D15" s="59" t="str">
+        <x:v>추적표 v1.5</x:v>
+      </x:c>
+      <x:c r="E15" s="59" t="str">
+        <x:v>배포 전 통합 확인</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/docs/최종 문서/e-학습터 개발 명세서.xlsx
+++ b/docs/최종 문서/e-학습터 개발 명세서.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="R9c48fd2d711044cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="R2237ed99d6974a6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="R37b4882d479945b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="R7b1c39e7c416435d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="R0d697a3c17c74cdf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="Rd49c1a84ce364f44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="R2ede08e03c964f25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="Ra2ad5c9c34ba444b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="R62caa21b029b4cdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="Ree377c4e5da94427"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="R1f05bd8f723541bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="Re73f70ab65894d01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="R78900055b9c04d4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="R37f083fe249041d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="R7b02a88fdbce4431"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="R2a3f74b5a3214945"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-12" sheetId="9" r:id="R877067a9baeb4e54"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,7 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="17">
+  <x:fonts count="20">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -106,8 +107,25 @@
       <x:color rgb="FF1F1F1F"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1F1F1F"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF404040"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF1F1F1F"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="20">
+  <x:fills count="23">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -204,6 +222,21 @@
         <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F8FC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="6">
     <x:border/>
@@ -282,7 +315,7 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="60">
+  <x:cellXfs count="73">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -426,6 +459,45 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="22" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -10998,4 +11070,251 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="21" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="61" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="62" t="str">
+        <x:v>개발 명세서 최신화 요약</x:v>
+      </x:c>
+      <x:c r="B1" s="62"/>
+      <x:c r="C1" s="62"/>
+      <x:c r="D1" s="62"/>
+      <x:c r="E1" s="62"/>
+    </x:row>
+    <x:row r="2" ht="36" customHeight="1">
+      <x:c r="A2" s="65" t="str">
+        <x:v>작성자: 이현겸 / 기준일:
+2026-07-12</x:v>
+      </x:c>
+      <x:c r="B2" s="65" t="str">
+        <x:v>REST API v2.1</x:v>
+      </x:c>
+      <x:c r="C2" s="65" t="str">
+        <x:v>MVC v2.1</x:v>
+      </x:c>
+      <x:c r="D2" s="65" t="str">
+        <x:v>화면 매핑 v0.14</x:v>
+      </x:c>
+      <x:c r="E2" s="65" t="str">
+        <x:v>화면 설계 v1.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="12" customHeight="1">
+      <x:c r="A3" s="43"/>
+      <x:c r="B3" s="43"/>
+      <x:c r="C3" s="43"/>
+      <x:c r="D3" s="43"/>
+      <x:c r="E3" s="43"/>
+    </x:row>
+    <x:row r="4" ht="26" customHeight="1">
+      <x:c r="A4" s="69" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B4" s="69" t="str">
+        <x:v>최신 기준</x:v>
+      </x:c>
+      <x:c r="C4" s="69" t="str">
+        <x:v>반영 내용</x:v>
+      </x:c>
+      <x:c r="D4" s="69" t="str">
+        <x:v>검증 근거</x:v>
+      </x:c>
+      <x:c r="E4" s="69" t="str">
+        <x:v>비고</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="62" customHeight="1">
+      <x:c r="A5" s="72" t="str">
+        <x:v>변경 성격</x:v>
+      </x:c>
+      <x:c r="B5" s="72" t="str">
+        <x:v>설계 최신화·UI/API</x:v>
+      </x:c>
+      <x:c r="C5" s="72" t="str">
+        <x:v>요구사항과 DB 구조를 바꾸지 않고, 공통 오류 화면과 오류 응답 경계를 실제 구현에 맞춰 명세·추적표에 연결</x:v>
+      </x:c>
+      <x:c r="D5" s="72" t="str">
+        <x:v>7/12 commit fdd86d3, Notion 재조회</x:v>
+      </x:c>
+      <x:c r="E5" s="72" t="str">
+        <x:v>SRS/DB 버전 유지</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="62" customHeight="1">
+      <x:c r="A6" s="72" t="str">
+        <x:v>오류 화면</x:v>
+      </x:c>
+      <x:c r="B6" s="72" t="str">
+        <x:v>403 / 404 / 500</x:v>
+      </x:c>
+      <x:c r="C6" s="72" t="str">
+        <x:v>상태별 direct route와 Thymeleaf view를 추가하고 Knowva 공통 fragment·theme CSS로 화면을 통일</x:v>
+      </x:c>
+      <x:c r="D6" s="72" t="str">
+        <x:v>ErrorPageController, error templates, page-error fragment</x:v>
+      </x:c>
+      <x:c r="E6" s="72" t="str">
+        <x:v>각 상태 code 반환</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="62" customHeight="1">
+      <x:c r="A7" s="72" t="str">
+        <x:v>HTML 오류</x:v>
+      </x:c>
+      <x:c r="B7" s="72" t="str">
+        <x:v>Accept 최우선 text/html</x:v>
+      </x:c>
+      <x:c r="C7" s="72" t="str">
+        <x:v>정적 리소스 미발견은 404, 미처리 예외는 500 ModelAndView로 처리</x:v>
+      </x:c>
+      <x:c r="D7" s="72" t="str">
+        <x:v>GlobalExceptionHandler</x:v>
+      </x:c>
+      <x:c r="E7" s="72" t="str">
+        <x:v>브라우저 화면 전용</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="62" customHeight="1">
+      <x:c r="A8" s="72" t="str">
+        <x:v>JSON API 오류</x:v>
+      </x:c>
+      <x:c r="B8" s="72" t="str">
+        <x:v>ApiResponse + application/json</x:v>
+      </x:c>
+      <x:c r="C8" s="72" t="str">
+        <x:v>HTML이 최우선이 아니거나 text/html;q=0이면 기존 API error code/status와 JSON body를 유지</x:v>
+      </x:c>
+      <x:c r="D8" s="72" t="str">
+        <x:v>GlobalExceptionHandler, REST API v2.1</x:v>
+      </x:c>
+      <x:c r="E8" s="72" t="str">
+        <x:v>API 화면 렌더 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="62" customHeight="1">
+      <x:c r="A9" s="72" t="str">
+        <x:v>Validation</x:v>
+      </x:c>
+      <x:c r="B9" s="72" t="str">
+        <x:v>binding failure 안전 문구</x:v>
+      </x:c>
+      <x:c r="C9" s="72" t="str">
+        <x:v>형식 변환 실패의 내부 Spring 메시지를 노출하지 않고 사용자 안내 문구로 반환</x:v>
+      </x:c>
+      <x:c r="D9" s="72" t="str">
+        <x:v>GlobalExceptionHandlerWebMvcTest</x:v>
+      </x:c>
+      <x:c r="E9" s="72" t="str">
+        <x:v>입력값 형식 오류</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="62" customHeight="1">
+      <x:c r="A10" s="72" t="str">
+        <x:v>공통 UI</x:v>
+      </x:c>
+      <x:c r="B10" s="72" t="str">
+        <x:v>page-error / error.css</x:v>
+      </x:c>
+      <x:c r="C10" s="72" t="str">
+        <x:v>상태 코드·안내·학습 홈·이전 페이지 CTA를 공통 fragment로 제공하고 light/dark theme 대비를 유지</x:v>
+      </x:c>
+      <x:c r="D10" s="72" t="str">
+        <x:v>templates/fragments/page-error.html, static/css/screens/error.css</x:v>
+      </x:c>
+      <x:c r="E10" s="72" t="str">
+        <x:v>DB 조회 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="62" customHeight="1">
+      <x:c r="A11" s="72" t="str">
+        <x:v>Notion 문서</x:v>
+      </x:c>
+      <x:c r="B11" s="72" t="str">
+        <x:v>REST v2.1 / MVC v2.1</x:v>
+      </x:c>
+      <x:c r="C11" s="72" t="str">
+        <x:v>화면 설계 v1.7, 매핑표 v0.14, 구현 변경 기록, 추적표 v1.6을 최신화</x:v>
+      </x:c>
+      <x:c r="D11" s="72" t="str">
+        <x:v>Notion fetch/update 재검증</x:v>
+      </x:c>
+      <x:c r="E11" s="72" t="str">
+        <x:v>7/12 일지와 연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="62" customHeight="1">
+      <x:c r="A12" s="72" t="str">
+        <x:v>WBS</x:v>
+      </x:c>
+      <x:c r="B12" s="72" t="str">
+        <x:v>MVP 이후 범위 재정렬</x:v>
+      </x:c>
+      <x:c r="C12" s="72" t="str">
+        <x:v>WBS-027 다음 확장 기능 WBS-028~035, 배포·운영 WBS-036~038의 연속 ID와 담당 범위를 확인</x:v>
+      </x:c>
+      <x:c r="D12" s="72" t="str">
+        <x:v>Google Sheets WBS_진행관리</x:v>
+      </x:c>
+      <x:c r="E12" s="72" t="str">
+        <x:v>정렬 확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="62" customHeight="1">
+      <x:c r="A13" s="72" t="str">
+        <x:v>검증</x:v>
+      </x:c>
+      <x:c r="B13" s="72" t="str">
+        <x:v>MVC test 추가</x:v>
+      </x:c>
+      <x:c r="C13" s="72" t="str">
+        <x:v>direct status/view, Accept 우선순위, HTML 거부 JSON 유지, binding failure 메시지 정제 test를 추가</x:v>
+      </x:c>
+      <x:c r="D13" s="72" t="str">
+        <x:v>ErrorPageControllerWebMvcTest, GlobalExceptionHandlerWebMvcTest</x:v>
+      </x:c>
+      <x:c r="E13" s="72" t="str">
+        <x:v>Gradle targeted test 실행</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="62" customHeight="1">
+      <x:c r="A14" s="72" t="str">
+        <x:v>다음 액션</x:v>
+      </x:c>
+      <x:c r="B14" s="72" t="str">
+        <x:v>통합 smoke test</x:v>
+      </x:c>
+      <x:c r="C14" s="72" t="str">
+        <x:v>브라우저 오류 화면과 API 오류 응답을 포함해 주요 사용자 흐름의 end-to-end smoke를 진행</x:v>
+      </x:c>
+      <x:c r="D14" s="72" t="str">
+        <x:v>추적표 v1.6</x:v>
+      </x:c>
+      <x:c r="E14" s="72" t="str">
+        <x:v>배포 전 통합 확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="43"/>
+      <x:c r="B15" s="43"/>
+      <x:c r="C15" s="43"/>
+      <x:c r="D15" s="43"/>
+      <x:c r="E15" s="43"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/docs/최종 문서/e-학습터 개발 명세서.xlsx
+++ b/docs/최종 문서/e-학습터 개발 명세서.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="R62caa21b029b4cdd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="Ree377c4e5da94427"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="R1f05bd8f723541bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="Re73f70ab65894d01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="R78900055b9c04d4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="R37f083fe249041d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="R7b02a88fdbce4431"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="R2a3f74b5a3214945"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-12" sheetId="9" r:id="R877067a9baeb4e54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="R14390348a9cd45b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="Re53f65d00c8a4288"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="R3ee4e3de858d4a32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="R3ef07858c22f4bd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="R7e23d17bf87d4489"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="Raeed07398cad4a62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="Rfc608710f08c432b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="Rc60f0db98a064271"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-12" sheetId="9" r:id="Rb52d46a55b5a4c08"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,7 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="20">
+  <x:fonts count="27">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -124,8 +124,48 @@
       <x:color rgb="FF1F1F1F"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF134E4A"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF9A3412"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF9A3412"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="23">
+  <x:fills count="29">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -237,8 +277,38 @@
         <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F766E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE6FFFA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF115E59"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF0FDFA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF7ED"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="6">
+  <x:borders count="8">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -310,12 +380,40 @@
         <x:color rgb="FFD9E2F3"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF99F6E4"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF99F6E4"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF99F6E4"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF99F6E4"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFFED7AA"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFFED7AA"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFFED7AA"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFFED7AA"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="73">
+  <x:cellXfs count="103">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -498,6 +596,96 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="25" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="25" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="25" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="26" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="26" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="26" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="26" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="28" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="28" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -11076,233 +11264,204 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="21" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="61" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="56" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="62" t="str">
-        <x:v>개발 명세서 최신화 요약</x:v>
-      </x:c>
-      <x:c r="B1" s="62"/>
-      <x:c r="C1" s="62"/>
-      <x:c r="D1" s="62"/>
-      <x:c r="E1" s="62"/>
-    </x:row>
-    <x:row r="2" ht="36" customHeight="1">
-      <x:c r="A2" s="65" t="str">
-        <x:v>작성자: 이현겸 / 기준일:
-2026-07-12</x:v>
-      </x:c>
-      <x:c r="B2" s="65" t="str">
-        <x:v>REST API v2.1</x:v>
-      </x:c>
-      <x:c r="C2" s="65" t="str">
-        <x:v>MVC v2.1</x:v>
-      </x:c>
-      <x:c r="D2" s="65" t="str">
-        <x:v>화면 매핑 v0.14</x:v>
-      </x:c>
-      <x:c r="E2" s="65" t="str">
-        <x:v>화면 설계 v1.7</x:v>
-      </x:c>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="76" t="str">
+        <x:v>2026.07.13 구현 최신화</x:v>
+      </x:c>
+      <x:c r="B1" s="76"/>
+      <x:c r="C1" s="76"/>
+      <x:c r="D1" s="76"/>
+      <x:c r="E1" s="76"/>
+    </x:row>
+    <x:row r="2" ht="40" customHeight="1">
+      <x:c r="A2" s="79" t="str">
+        <x:v>기준: 2026-07-13 merge PR #125-#136 및 DDL v2.3. 구현된 동작만 기록하며, 미구현 환불 API와 관리자 API 권한 보강은 별도 리스크로 남긴다.</x:v>
+      </x:c>
+      <x:c r="B2" s="79"/>
+      <x:c r="C2" s="79"/>
+      <x:c r="D2" s="79"/>
+      <x:c r="E2" s="79"/>
     </x:row>
     <x:row r="3" ht="12" customHeight="1">
-      <x:c r="A3" s="43"/>
-      <x:c r="B3" s="43"/>
-      <x:c r="C3" s="43"/>
-      <x:c r="D3" s="43"/>
-      <x:c r="E3" s="43"/>
-    </x:row>
-    <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="69" t="str">
-        <x:v>구분</x:v>
-      </x:c>
-      <x:c r="B4" s="69" t="str">
-        <x:v>최신 기준</x:v>
-      </x:c>
-      <x:c r="C4" s="69" t="str">
-        <x:v>반영 내용</x:v>
-      </x:c>
-      <x:c r="D4" s="69" t="str">
-        <x:v>검증 근거</x:v>
-      </x:c>
-      <x:c r="E4" s="69" t="str">
-        <x:v>비고</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="62" customHeight="1">
-      <x:c r="A5" s="72" t="str">
-        <x:v>변경 성격</x:v>
-      </x:c>
-      <x:c r="B5" s="72" t="str">
-        <x:v>설계 최신화·UI/API</x:v>
-      </x:c>
-      <x:c r="C5" s="72" t="str">
-        <x:v>요구사항과 DB 구조를 바꾸지 않고, 공통 오류 화면과 오류 응답 경계를 실제 구현에 맞춰 명세·추적표에 연결</x:v>
-      </x:c>
-      <x:c r="D5" s="72" t="str">
-        <x:v>7/12 commit fdd86d3, Notion 재조회</x:v>
-      </x:c>
-      <x:c r="E5" s="72" t="str">
-        <x:v>SRS/DB 버전 유지</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="62" customHeight="1">
-      <x:c r="A6" s="72" t="str">
-        <x:v>오류 화면</x:v>
-      </x:c>
-      <x:c r="B6" s="72" t="str">
-        <x:v>403 / 404 / 500</x:v>
-      </x:c>
-      <x:c r="C6" s="72" t="str">
-        <x:v>상태별 direct route와 Thymeleaf view를 추가하고 Knowva 공통 fragment·theme CSS로 화면을 통일</x:v>
-      </x:c>
-      <x:c r="D6" s="72" t="str">
-        <x:v>ErrorPageController, error templates, page-error fragment</x:v>
-      </x:c>
-      <x:c r="E6" s="72" t="str">
-        <x:v>각 상태 code 반환</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="62" customHeight="1">
-      <x:c r="A7" s="72" t="str">
-        <x:v>HTML 오류</x:v>
-      </x:c>
-      <x:c r="B7" s="72" t="str">
-        <x:v>Accept 최우선 text/html</x:v>
-      </x:c>
-      <x:c r="C7" s="72" t="str">
-        <x:v>정적 리소스 미발견은 404, 미처리 예외는 500 ModelAndView로 처리</x:v>
-      </x:c>
-      <x:c r="D7" s="72" t="str">
-        <x:v>GlobalExceptionHandler</x:v>
-      </x:c>
-      <x:c r="E7" s="72" t="str">
-        <x:v>브라우저 화면 전용</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="62" customHeight="1">
-      <x:c r="A8" s="72" t="str">
-        <x:v>JSON API 오류</x:v>
-      </x:c>
-      <x:c r="B8" s="72" t="str">
-        <x:v>ApiResponse + application/json</x:v>
-      </x:c>
-      <x:c r="C8" s="72" t="str">
-        <x:v>HTML이 최우선이 아니거나 text/html;q=0이면 기존 API error code/status와 JSON body를 유지</x:v>
-      </x:c>
-      <x:c r="D8" s="72" t="str">
-        <x:v>GlobalExceptionHandler, REST API v2.1</x:v>
-      </x:c>
-      <x:c r="E8" s="72" t="str">
-        <x:v>API 화면 렌더 없음</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="62" customHeight="1">
-      <x:c r="A9" s="72" t="str">
-        <x:v>Validation</x:v>
-      </x:c>
-      <x:c r="B9" s="72" t="str">
-        <x:v>binding failure 안전 문구</x:v>
-      </x:c>
-      <x:c r="C9" s="72" t="str">
-        <x:v>형식 변환 실패의 내부 Spring 메시지를 노출하지 않고 사용자 안내 문구로 반환</x:v>
-      </x:c>
-      <x:c r="D9" s="72" t="str">
-        <x:v>GlobalExceptionHandlerWebMvcTest</x:v>
-      </x:c>
-      <x:c r="E9" s="72" t="str">
-        <x:v>입력값 형식 오류</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="62" customHeight="1">
-      <x:c r="A10" s="72" t="str">
-        <x:v>공통 UI</x:v>
-      </x:c>
-      <x:c r="B10" s="72" t="str">
-        <x:v>page-error / error.css</x:v>
-      </x:c>
-      <x:c r="C10" s="72" t="str">
-        <x:v>상태 코드·안내·학습 홈·이전 페이지 CTA를 공통 fragment로 제공하고 light/dark theme 대비를 유지</x:v>
-      </x:c>
-      <x:c r="D10" s="72" t="str">
-        <x:v>templates/fragments/page-error.html, static/css/screens/error.css</x:v>
-      </x:c>
-      <x:c r="E10" s="72" t="str">
-        <x:v>DB 조회 없음</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="62" customHeight="1">
-      <x:c r="A11" s="72" t="str">
-        <x:v>Notion 문서</x:v>
-      </x:c>
-      <x:c r="B11" s="72" t="str">
-        <x:v>REST v2.1 / MVC v2.1</x:v>
-      </x:c>
-      <x:c r="C11" s="72" t="str">
-        <x:v>화면 설계 v1.7, 매핑표 v0.14, 구현 변경 기록, 추적표 v1.6을 최신화</x:v>
-      </x:c>
-      <x:c r="D11" s="72" t="str">
-        <x:v>Notion fetch/update 재검증</x:v>
-      </x:c>
-      <x:c r="E11" s="72" t="str">
-        <x:v>7/12 일지와 연결</x:v>
+      <x:c r="A3" s="84" t="str">
+        <x:v>분류</x:v>
+      </x:c>
+      <x:c r="B3" s="84" t="str">
+        <x:v>범위</x:v>
+      </x:c>
+      <x:c r="C3" s="84" t="str">
+        <x:v>구현 기준</x:v>
+      </x:c>
+      <x:c r="D3" s="84" t="str">
+        <x:v>대표 route / source</x:v>
+      </x:c>
+      <x:c r="E3" s="84" t="str">
+        <x:v>DB / 상태</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="58" customHeight="1">
+      <x:c r="A4" s="95" t="str">
+        <x:v>인증 / 보안</x:v>
+      </x:c>
+      <x:c r="B4" s="91" t="str">
+        <x:v>비밀번호 재설정</x:v>
+      </x:c>
+      <x:c r="C4" s="91" t="str">
+        <x:v>이메일/비밀번호 계정만 재설정 링크 발급. 토큰은 SHA-256 hash만 저장하고 30분 만료, 1회 사용, 60초 재전송 제한을 적용한다.</x:v>
+      </x:c>
+      <x:c r="D4" s="91" t="str">
+        <x:v>GET/POST /password/forgot, GET/POST /password/reset</x:v>
+      </x:c>
+      <x:c r="E4" s="91" t="str">
+        <x:v>password_reset_tokens · 구현 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="58" customHeight="1">
+      <x:c r="A5" s="96" t="str">
+        <x:v>학습</x:v>
+      </x:c>
+      <x:c r="B5" s="92" t="str">
+        <x:v>과목 수강신청 / 시작 분기</x:v>
+      </x:c>
+      <x:c r="C5" s="92" t="str">
+        <x:v>과목 소개에서 BASIC 또는 LEVEL_TEST 시작 방식을 선택한다. BASIC은 BRONZE 해금 후 학습으로, LEVEL_TEST는 시험 시작으로 연결한다.</x:v>
+      </x:c>
+      <x:c r="D5" s="92" t="str">
+        <x:v>GET /learning/subjects/{id}, POST /learning/subjects/{id}/enroll</x:v>
+      </x:c>
+      <x:c r="E5" s="92" t="str">
+        <x:v>user_subject_enrollments · 구현 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="58" customHeight="1">
+      <x:c r="A6" s="96" t="str">
+        <x:v>문제풀이</x:v>
+      </x:c>
+      <x:c r="B6" s="92" t="str">
+        <x:v>문항 이동 / 건너뛰기</x:v>
+      </x:c>
+      <x:c r="C6" s="92" t="str">
+        <x:v>이전·다음·건너뛰기를 제공한다. 마지막 문제 건너뛰기는 확인 뒤 종료하며, skipped는 점수·오답 복습 대상에서 제외한다.</x:v>
+      </x:c>
+      <x:c r="D6" s="92" t="str">
+        <x:v>POST /learning/practice/sets/{setAttemptId}/skip</x:v>
+      </x:c>
+      <x:c r="E6" s="92" t="str">
+        <x:v>practice_submissions.is_skipped · 구현 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="58" customHeight="1">
+      <x:c r="A7" s="96" t="str">
+        <x:v>AI 시험 / 분석</x:v>
+      </x:c>
+      <x:c r="B7" s="92" t="str">
+        <x:v>레슨 단위 출제 / 중복 방지</x:v>
+      </x:c>
+      <x:c r="C7" s="92" t="str">
+        <x:v>활성 필수 레슨의 이론과 문제풀이를 모두 완료한 범위만 출제한다. 진행 중인 동일 시험은 재사용하고 분석은 사용자·시험당 1건으로 생성한다.</x:v>
+      </x:c>
+      <x:c r="D7" s="92" t="str">
+        <x:v>GET /api/exams/eligibility, POST /api/exams, POST /api/analyses</x:v>
+      </x:c>
+      <x:c r="E7" s="92" t="str">
+        <x:v>exam/analysis mapper · 구현 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="58" customHeight="1">
+      <x:c r="A8" s="96" t="str">
+        <x:v>결제 / Premium</x:v>
+      </x:c>
+      <x:c r="B8" s="92" t="str">
+        <x:v>Toss 카드 승인 / 환불 이력</x:v>
+      </x:c>
+      <x:c r="C8" s="92" t="str">
+        <x:v>Toss ready에서 PENDING 주문을 만들고 승인 성공 뒤 PAID와 Premium grant를 기록한다. 결제 이력은 PAID만 노출한다. 환불은 DB 이력만 추가됐고 API/MVC는 미구현이다.</x:v>
+      </x:c>
+      <x:c r="D8" s="92" t="str">
+        <x:v>POST /api/payments/toss/ready, GET /payments/toss/{success,fail}</x:v>
+      </x:c>
+      <x:c r="E8" s="92" t="str">
+        <x:v>dummy_payments, payment_refunds · 일부 구현</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="58" customHeight="1">
+      <x:c r="A9" s="96" t="str">
+        <x:v>회원 / 마이페이지</x:v>
+      </x:c>
+      <x:c r="B9" s="92" t="str">
+        <x:v>소셜 가입 / 탈퇴 / 수강 상태</x:v>
+      </x:c>
+      <x:c r="C9" s="92" t="str">
+        <x:v>소셜 가입은 추가 정보 입력 뒤 생성한다. 탈퇴는 soft delete+masking이며, 대표 과목은 ACTIVE 수강 과목으로 제한한다.</x:v>
+      </x:c>
+      <x:c r="D9" s="92" t="str">
+        <x:v>GET/POST /oauth/signup, GET /mypage</x:v>
+      </x:c>
+      <x:c r="E9" s="92" t="str">
+        <x:v>users, social_accounts, user_subject_enrollments · 구현 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="58" customHeight="1">
+      <x:c r="A10" s="96" t="str">
+        <x:v>관리자</x:v>
+      </x:c>
+      <x:c r="B10" s="92" t="str">
+        <x:v>운영 로그 / 콘텐츠·커뮤니티 상태</x:v>
+      </x:c>
+      <x:c r="C10" s="92" t="str">
+        <x:v>운영 로그는 대상·작업 분류 필터와 페이지네이션을 제공한다. 과목 비활성화는 하위 콘텐츠 접근을 제한하고 상태를 복원한다. 게시글·댓글은 ACTIVE/HIDDEN/DELETED만 허용한다.</x:v>
+      </x:c>
+      <x:c r="D10" s="92" t="str">
+        <x:v>GET /admin/operation-logs, PATCH /api/admin/community/**/status</x:v>
+      </x:c>
+      <x:c r="E10" s="92" t="str">
+        <x:v>admin_operation_logs, subject_content_status_backups · 구현 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="58" customHeight="1">
+      <x:c r="A11" s="101" t="str">
+        <x:v>확인 필요</x:v>
+      </x:c>
+      <x:c r="B11" s="102" t="str">
+        <x:v>관리자 API 권한</x:v>
+      </x:c>
+      <x:c r="C11" s="102" t="str">
+        <x:v>MVC /admin/**는 관리자 interceptor로 보호한다. /api/admin/**는 별도 ROLE_ADMIN 검증 보강이 필요하다.</x:v>
+      </x:c>
+      <x:c r="D11" s="102" t="str">
+        <x:v>/api/admin/**</x:v>
+      </x:c>
+      <x:c r="E11" s="102" t="str">
+        <x:v>추적 리스크</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="62" customHeight="1">
-      <x:c r="A12" s="72" t="str">
-        <x:v>WBS</x:v>
-      </x:c>
-      <x:c r="B12" s="72" t="str">
-        <x:v>MVP 이후 범위 재정렬</x:v>
-      </x:c>
-      <x:c r="C12" s="72" t="str">
-        <x:v>WBS-027 다음 확장 기능 WBS-028~035, 배포·운영 WBS-036~038의 연속 ID와 담당 범위를 확인</x:v>
-      </x:c>
-      <x:c r="D12" s="72" t="str">
-        <x:v>Google Sheets WBS_진행관리</x:v>
-      </x:c>
-      <x:c r="E12" s="72" t="str">
-        <x:v>정렬 확인</x:v>
-      </x:c>
+      <x:c r="A12" s="72"/>
+      <x:c r="B12" s="72"/>
+      <x:c r="C12" s="72"/>
+      <x:c r="D12" s="72"/>
+      <x:c r="E12" s="72"/>
     </x:row>
     <x:row r="13" ht="62" customHeight="1">
-      <x:c r="A13" s="72" t="str">
-        <x:v>검증</x:v>
-      </x:c>
-      <x:c r="B13" s="72" t="str">
-        <x:v>MVC test 추가</x:v>
-      </x:c>
-      <x:c r="C13" s="72" t="str">
-        <x:v>direct status/view, Accept 우선순위, HTML 거부 JSON 유지, binding failure 메시지 정제 test를 추가</x:v>
-      </x:c>
-      <x:c r="D13" s="72" t="str">
-        <x:v>ErrorPageControllerWebMvcTest, GlobalExceptionHandlerWebMvcTest</x:v>
-      </x:c>
-      <x:c r="E13" s="72" t="str">
-        <x:v>Gradle targeted test 실행</x:v>
-      </x:c>
+      <x:c r="A13" s="72"/>
+      <x:c r="B13" s="72"/>
+      <x:c r="C13" s="72"/>
+      <x:c r="D13" s="72"/>
+      <x:c r="E13" s="72"/>
     </x:row>
     <x:row r="14" ht="62" customHeight="1">
-      <x:c r="A14" s="72" t="str">
-        <x:v>다음 액션</x:v>
-      </x:c>
-      <x:c r="B14" s="72" t="str">
-        <x:v>통합 smoke test</x:v>
-      </x:c>
-      <x:c r="C14" s="72" t="str">
-        <x:v>브라우저 오류 화면과 API 오류 응답을 포함해 주요 사용자 흐름의 end-to-end smoke를 진행</x:v>
-      </x:c>
-      <x:c r="D14" s="72" t="str">
-        <x:v>추적표 v1.6</x:v>
-      </x:c>
-      <x:c r="E14" s="72" t="str">
-        <x:v>배포 전 통합 확인</x:v>
-      </x:c>
+      <x:c r="A14" s="72"/>
+      <x:c r="B14" s="72"/>
+      <x:c r="C14" s="72"/>
+      <x:c r="D14" s="72"/>
+      <x:c r="E14" s="72"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="43"/>
@@ -11314,6 +11473,7 @@
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/docs/최종 문서/e-학습터 개발 명세서.xlsx
+++ b/docs/최종 문서/e-학습터 개발 명세서.xlsx
@@ -2,15 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="R14390348a9cd45b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="Re53f65d00c8a4288"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="R3ee4e3de858d4a32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="R3ef07858c22f4bd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="R7e23d17bf87d4489"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="Raeed07398cad4a62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="Rfc608710f08c432b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="Rc60f0db98a064271"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-12" sheetId="9" r:id="Rb52d46a55b5a4c08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="Rc48dc5ed47784422"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="R7e54db00ab20439f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="R479580d600214a96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="R947f4e967efb4416"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="Rb63b9d7170104a00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="R8db2571ac8af44ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="R5e352565bee04831"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="R942988bbbc144300"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-12" sheetId="9" r:id="R8bd5cb05bda94cc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-14" sheetId="10" r:id="R6fc750abaef24b63"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="27">
+  <x:fonts count="28">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -164,8 +165,13 @@
       <x:color rgb="FF9A3412"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF0D5356"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="29">
+  <x:fills count="32">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -307,8 +313,23 @@
         <x:fgColor rgb="FFFFF7ED"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF117D79"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDF1EF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F776F"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="8">
+  <x:borders count="9">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -408,12 +429,26 @@
         <x:color rgb="FFFED7AA"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC7DCE7"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFC7DCE7"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFC7DCE7"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFC7DCE7"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="103">
+  <x:cellXfs count="123">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -686,6 +721,52 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="26" fillId="28" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="31" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -5155,6 +5236,235 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="17" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="66" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="36" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="106" t="str">
+        <x:v>2026.07.14 구현 최신화</x:v>
+      </x:c>
+      <x:c r="B1" s="106"/>
+      <x:c r="C1" s="106"/>
+      <x:c r="D1" s="106"/>
+      <x:c r="E1" s="106"/>
+    </x:row>
+    <x:row r="2" ht="34" customHeight="1">
+      <x:c r="A2" s="110" t="str">
+        <x:v>기준: 2026-07-14 병합 PR #137~#143 및 당일 commit. 요구사항·DB schema 변경 없이 구현된 사용자 흐름과 문서 정합성만 반영.</x:v>
+      </x:c>
+      <x:c r="B2" s="110"/>
+      <x:c r="C2" s="110"/>
+      <x:c r="D2" s="110"/>
+      <x:c r="E2" s="110"/>
+    </x:row>
+    <x:row r="3" ht="23" customHeight="1">
+      <x:c r="A3" s="120" t="str">
+        <x:v>분류</x:v>
+      </x:c>
+      <x:c r="B3" s="120" t="str">
+        <x:v>범위</x:v>
+      </x:c>
+      <x:c r="C3" s="120" t="str">
+        <x:v>구현 기준</x:v>
+      </x:c>
+      <x:c r="D3" s="120" t="str">
+        <x:v>대표 route / source</x:v>
+      </x:c>
+      <x:c r="E3" s="120" t="str">
+        <x:v>DB / 상태</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="24" hidden="0" customHeight="1">
+      <x:c r="A4" s="121" t="str">
+        <x:v>학습</x:v>
+      </x:c>
+      <x:c r="B4" s="121" t="str">
+        <x:v>수강 시작·학습 API 인증</x:v>
+      </x:c>
+      <x:c r="C4" s="122" t="str">
+        <x:v>잠긴 로드맵을 열람한 뒤 과목 상세에서 BASIC 또는 LEVEL_TEST 시작 방식을 선택한다. 등록 과목 중심으로 학습하고 과목 추가를 제공하며, 학습 API는 session 인증을 강제한다.</x:v>
+      </x:c>
+      <x:c r="D4" s="122" t="str">
+        <x:v>GET /learning, GET/POST /learning/subjects/{subjectId}, GET /api/subjects, GET /api/level-tests/questions</x:v>
+      </x:c>
+      <x:c r="E4" s="122" t="str">
+        <x:v>user_subject_enrollments, user_level_unlocks · 구현 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="24" hidden="0" customHeight="1">
+      <x:c r="A5" s="121" t="str">
+        <x:v>학습</x:v>
+      </x:c>
+      <x:c r="B5" s="121" t="str">
+        <x:v>행성·레벨 달성 연출</x:v>
+      </x:c>
+      <x:c r="C5" s="122" t="str">
+        <x:v>기준선 이후 행성 완료 또는 실제 레벨 해금이 증가했을 때 한 번만 축하 overlay를 표시한다. 닫기 버튼·바깥 영역·ESC와 reduced motion을 지원한다.</x:v>
+      </x:c>
+      <x:c r="D5" s="122" t="str">
+        <x:v>LearningController, CelebrationView, learning-celebration.js</x:v>
+      </x:c>
+      <x:c r="E5" s="122" t="str">
+        <x:v>learning_progress, user_level_unlocks · 구현 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="24" hidden="0" customHeight="1">
+      <x:c r="A6" s="121" t="str">
+        <x:v>문제풀이/오답</x:v>
+      </x:c>
+      <x:c r="B6" s="121" t="str">
+        <x:v>문제 이동·완료 요약</x:v>
+      </x:c>
+      <x:c r="C6" s="122" t="str">
+        <x:v>문제풀이와 오답 복습에서 이전·다음·건너뛰기·마지막 완료 확인을 제공하고, 완료 요약 카드로 상태를 표시한다.</x:v>
+      </x:c>
+      <x:c r="D6" s="122" t="str">
+        <x:v>PracticeController, ReviewController, PracticeApiController</x:v>
+      </x:c>
+      <x:c r="E6" s="122" t="str">
+        <x:v>practice_set_attempts, practice_submissions, wrong_answers · 구현 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="24" hidden="0" customHeight="1">
+      <x:c r="A7" s="121" t="str">
+        <x:v>AI 시험/분석</x:v>
+      </x:c>
+      <x:c r="B7" s="121" t="str">
+        <x:v>starterCode 입력 경계·최종 제출</x:v>
+      </x:c>
+      <x:c r="C7" s="122" t="str">
+        <x:v>AI 원본 starterCode에 정답 로직이 있어도 학습자 editor와 분석 AI에는 서버 공통 TODO 골격만 전달한다. DB literal \n prompt는 줄바꿈으로 정규화하고, 문제별 제출 뒤 최종 제출 확인 모달을 표시한다.</x:v>
+      </x:c>
+      <x:c r="D7" s="122" t="str">
+        <x:v>ExamStarterCodeResolver, ExamPromptNormalizer, ExamController, AiAnalysisService</x:v>
+      </x:c>
+      <x:c r="E7" s="122" t="str">
+        <x:v>exam_sessions, ai_exam_problems, exam_answers, ai_analysis_reports · 구현 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="24" hidden="0" customHeight="1">
+      <x:c r="A8" s="121" t="str">
+        <x:v>커뮤니티</x:v>
+      </x:c>
+      <x:c r="B8" s="121" t="str">
+        <x:v>인기글·추천 콘텐츠</x:v>
+      </x:c>
+      <x:c r="C8" s="122" t="str">
+        <x:v>커뮤니티 홈에 인기글 배지를 반영하고, 관리자는 추천 콘텐츠를 조회·등록·수정·삭제한다.</x:v>
+      </x:c>
+      <x:c r="D8" s="122" t="str">
+        <x:v>community service/controller, AdminRecommendationController</x:v>
+      </x:c>
+      <x:c r="E8" s="122" t="str">
+        <x:v>community_posts, content_recommendations · 구현 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="24" hidden="0" customHeight="1">
+      <x:c r="A9" s="121" t="str">
+        <x:v>결제/Premium</x:v>
+      </x:c>
+      <x:c r="B9" s="121" t="str">
+        <x:v>실제 PG 환불</x:v>
+      </x:c>
+      <x:c r="C9" s="122" t="str">
+        <x:v>결제 소유자가 환불을 요청하면 카카오페이 또는 토스페이먼츠 취소 성공 후 환불 상태를 완료하고 Premium 권한을 회수한다.</x:v>
+      </x:c>
+      <x:c r="D9" s="122" t="str">
+        <x:v>POST /api/payments/{paymentId}/refund, PaymentRefundService, KakaoPayService, TossPaymentService</x:v>
+      </x:c>
+      <x:c r="E9" s="122" t="str">
+        <x:v>dummy_payments, payment_refunds, premium_grants · 구현 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="24" hidden="0" customHeight="1">
+      <x:c r="A10" s="121" t="str">
+        <x:v>문서 정합성</x:v>
+      </x:c>
+      <x:c r="B10" s="121" t="str">
+        <x:v>Notion·개발 명세서</x:v>
+      </x:c>
+      <x:c r="C10" s="122" t="str">
+        <x:v>구현 변경 기록, REST v2.3, MVC v2.3, 화면 설계 v1.9, 매핑표 v0.16, 확장 기능 범위 v0.7과 이 최신화 시트를 7/14 구현 기준으로 동기화했다.</x:v>
+      </x:c>
+      <x:c r="D10" s="122" t="str">
+        <x:v>Notion direct fetch/update, local git log, GitHub PR #137~#143</x:v>
+      </x:c>
+      <x:c r="E10" s="122" t="str">
+        <x:v>DDL/sample data 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="24" hidden="0" customHeight="1">
+      <x:c r="A11" s="121" t="str">
+        <x:v>검증</x:v>
+      </x:c>
+      <x:c r="B11" s="121" t="str">
+        <x:v>문서-구현 대조</x:v>
+      </x:c>
+      <x:c r="C11" s="122" t="str">
+        <x:v>SRS와 요구사항은 당일 변경 없음으로 유지하고, REST API·MVC·화면·매핑·개발 명세서에 구현 변경을 반영한다.</x:v>
+      </x:c>
+      <x:c r="D11" s="122" t="str">
+        <x:v>LearningApiController, PaymentApiController, source/controller·service 확인</x:v>
+      </x:c>
+      <x:c r="E11" s="122" t="str">
+        <x:v>통합 UI/실 PG sandbox 검증은 별도 수행</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="24" hidden="0" customHeight="1">
+      <x:c r="A12" s="121" t="str">
+        <x:v>다음 액션</x:v>
+      </x:c>
+      <x:c r="B12" s="121" t="str">
+        <x:v>통합 검증</x:v>
+      </x:c>
+      <x:c r="C12" s="122" t="str">
+        <x:v>로그인 상태 학습 시작, 문제풀이/오답 복습, AI 시험, 환불, 관리자 추천 콘텐츠의 end-to-end smoke test를 수행한다.</x:v>
+      </x:c>
+      <x:c r="D12" s="122" t="str">
+        <x:v>7/14 구현 변경 기록 / 프로젝트 일지</x:v>
+      </x:c>
+      <x:c r="E12" s="122" t="str">
+        <x:v>문서 최신화 완료</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>

--- a/docs/최종 문서/e-학습터 개발 명세서.xlsx
+++ b/docs/최종 문서/e-학습터 개발 명세서.xlsx
@@ -2,16 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="Rc48dc5ed47784422"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="R7e54db00ab20439f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="R479580d600214a96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="R947f4e967efb4416"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="Rb63b9d7170104a00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="R8db2571ac8af44ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="R5e352565bee04831"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="R942988bbbc144300"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-12" sheetId="9" r:id="R8bd5cb05bda94cc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-14" sheetId="10" r:id="R6fc750abaef24b63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="R96139bca99894f7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="R7f1b71df60a34d59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="R24f667d0965844cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="R2c36cf6b8f724ed0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="Rb316f2562c304895"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="Rbcdd3ad4d4ea435e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="R8f0c7d410d6c4942"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="R66587c56d09f499f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-12" sheetId="9" r:id="R01b391eebd4a4944"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-14" sheetId="10" r:id="Rf7a4c41752844591"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-15" sheetId="11" r:id="R2f39b016691c4c24"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22,7 +23,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="28">
+  <x:fonts count="33">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -170,8 +171,36 @@
       <x:color rgb="FF0D5356"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="18"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF185E63"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF18434B"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF175E63"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF185E63"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="32">
+  <x:fills count="36">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -328,8 +357,28 @@
         <x:fgColor rgb="FF0F776F"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF11827F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDF0EF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF0F8F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF8FCFC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="9">
+  <x:borders count="10">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -443,12 +492,26 @@
         <x:color rgb="FFC7DCE7"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB8D6D5"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFB8D6D5"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFB8D6D5"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB8D6D5"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="123">
+  <x:cellXfs count="146">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -768,6 +831,61 @@
     <x:xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="34" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="34" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="35" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="35" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="35" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="표준" xfId="0"/>
@@ -5465,6 +5583,197 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="72" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="47" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="36" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="126" t="str">
+        <x:v>2026.07.15 구현 최신화</x:v>
+      </x:c>
+      <x:c r="B1" s="126"/>
+      <x:c r="C1" s="126"/>
+      <x:c r="D1" s="126"/>
+      <x:c r="E1" s="126"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="131" t="str">
+        <x:v>기준: 2026-07-15 병합 PR #144~#150 및 DB 후속 커밋. 요구사항 변경 없이 구현 흐름·문서 정합성을 최신화.</x:v>
+      </x:c>
+      <x:c r="B2" s="131"/>
+      <x:c r="C2" s="131"/>
+      <x:c r="D2" s="131"/>
+      <x:c r="E2" s="131"/>
+    </x:row>
+    <x:row r="3" ht="26" customHeight="1">
+      <x:c r="A3" s="135" t="str">
+        <x:v>분류</x:v>
+      </x:c>
+      <x:c r="B3" s="135" t="str">
+        <x:v>범위</x:v>
+      </x:c>
+      <x:c r="C3" s="135" t="str">
+        <x:v>구현 기준</x:v>
+      </x:c>
+      <x:c r="D3" s="135" t="str">
+        <x:v>대표 route / source</x:v>
+      </x:c>
+      <x:c r="E3" s="135" t="str">
+        <x:v>DB / 상태</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="70" customHeight="1">
+      <x:c r="A4" s="142" t="str">
+        <x:v>커뮤니티·DB</x:v>
+      </x:c>
+      <x:c r="B4" s="145" t="str">
+        <x:v>댓글 숨김/삭제 상태</x:v>
+      </x:c>
+      <x:c r="C4" s="139" t="str">
+        <x:v>관리자 삭제는 처리자 ID를 저장하고 공개 복구 시 삭제 시각·처리자 ID를 함께 초기화한다. 숨김 게시글은 상세 접근을 막고, 삭제·숨김 댓글은 상태별 안내 문구로 표시한다.</x:v>
+      </x:c>
+      <x:c r="D4" s="139" t="str">
+        <x:v>AdminCommunityService, CommentService, PostService, CommentMapper.xml</x:v>
+      </x:c>
+      <x:c r="E4" s="139" t="str">
+        <x:v>comments.deleted_by_admin_id · 구현 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="70" customHeight="1">
+      <x:c r="A5" s="142" t="str">
+        <x:v>랭킹</x:v>
+      </x:c>
+      <x:c r="B5" s="145" t="str">
+        <x:v>주간/월간·통합/과목</x:v>
+      </x:c>
+      <x:c r="C5" s="139" t="str">
+        <x:v>랭킹 조회와 내 랭킹은 periodType 기본 WEEKLY로 주간 또는 월간을 선택한다. 출석·streak 점수는 제외하고 문제풀이·시험·일일 학습 점수를 표시한다.</x:v>
+      </x:c>
+      <x:c r="D5" s="139" t="str">
+        <x:v>GET /rankings, GET /api/rankings, GET /api/rankings/me, RankingService</x:v>
+      </x:c>
+      <x:c r="E5" s="139" t="str">
+        <x:v>ranking_scores, score_events, user_lesson_progress · 구현 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="70" customHeight="1">
+      <x:c r="A6" s="142" t="str">
+        <x:v>웰컴/튜토리얼</x:v>
+      </x:c>
+      <x:c r="B6" s="145" t="str">
+        <x:v>단계별 서비스 소개</x:v>
+      </x:c>
+      <x:c r="C6" s="139" t="str">
+        <x:v>단계별 이미지·누비 포즈/위치·기능 하이라이트·말풍선을 서버 view data로 전달하고 슬라이드 overlay를 갱신한다.</x:v>
+      </x:c>
+      <x:c r="D6" s="139" t="str">
+        <x:v>WelcomeController, TutorialStepView, welcome/index, welcome-tutorial.js</x:v>
+      </x:c>
+      <x:c r="E6" s="139" t="str">
+        <x:v>저장 없음 · 구현 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="70" customHeight="1">
+      <x:c r="A7" s="142" t="str">
+        <x:v>마이페이지·결제</x:v>
+      </x:c>
+      <x:c r="B7" s="145" t="str">
+        <x:v>진행률·결제 상세</x:v>
+      </x:c>
+      <x:c r="C7" s="139" t="str">
+        <x:v>전체 과목은 Bronze·Silver·Gold 진행률 평균을 하나의 진행률로 표시한다. 결제 상세는 결제·거래·Premium 권한·환불 정보를 구획한다.</x:v>
+      </x:c>
+      <x:c r="D7" s="139" t="str">
+        <x:v>LearningStatusPageResponse, settings/payment.html</x:v>
+      </x:c>
+      <x:c r="E7" s="139" t="str">
+        <x:v>learning progress, dummy_payments, payment_refunds, premium_grants · 구현 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="70" customHeight="1">
+      <x:c r="A8" s="142" t="str">
+        <x:v>관리자·UI</x:v>
+      </x:c>
+      <x:c r="B8" s="145" t="str">
+        <x:v>추천 콘텐츠·문제풀이</x:v>
+      </x:c>
+      <x:c r="C8" s="139" t="str">
+        <x:v>추천 콘텐츠 목록은 등록일과 실제 수정일을 분리한다. 문제풀이 시작·랭킹 화면은 카드형 정보 구조와 캐릭터 asset을 사용한다.</x:v>
+      </x:c>
+      <x:c r="D8" s="139" t="str">
+        <x:v>AdminRecommendationService, recommendations.html, practice.html, ranking/index.html</x:v>
+      </x:c>
+      <x:c r="E8" s="139" t="str">
+        <x:v>content_recommendations · 구현 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="70" customHeight="1">
+      <x:c r="A9" s="142" t="str">
+        <x:v>문서 정합성</x:v>
+      </x:c>
+      <x:c r="B9" s="145" t="str">
+        <x:v>Notion / DB / 최종 문서</x:v>
+      </x:c>
+      <x:c r="C9" s="139" t="str">
+        <x:v>DB v2.4, REST v2.4, MVC v2.4, 화면 설계 v2.0, 매핑표 v0.17, 추적표 v1.9와 이 시트를 7/15 근거로 연결한다.</x:v>
+      </x:c>
+      <x:c r="D9" s="139" t="str">
+        <x:v>Notion direct fetch/update, Knowva_DDL.sql, Knowva_sample_data.sql, ERD</x:v>
+      </x:c>
+      <x:c r="E9" s="139" t="str">
+        <x:v>정합성 확인 완료</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="70" customHeight="1">
+      <x:c r="A10" s="142" t="str">
+        <x:v>검증</x:v>
+      </x:c>
+      <x:c r="B10" s="145" t="str">
+        <x:v>문서·코드 근거</x:v>
+      </x:c>
+      <x:c r="C10" s="139" t="str">
+        <x:v>GitHub merged PR #144~#150과 target-date commits를 대조했다. 현재 7/16 미커밋 자유 코딩·커뮤니티 seed 변경은 이 시트의 7/15 범위에서 제외한다.</x:v>
+      </x:c>
+      <x:c r="D10" s="139" t="str">
+        <x:v>git log 2026-07-15, GitHub PR metadata, Notion fetch</x:v>
+      </x:c>
+      <x:c r="E10" s="139" t="str">
+        <x:v>근거 확인 완료</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="70" customHeight="1">
+      <x:c r="A11" s="142" t="str">
+        <x:v>다음 액션</x:v>
+      </x:c>
+      <x:c r="B11" s="145" t="str">
+        <x:v>통합 검증</x:v>
+      </x:c>
+      <x:c r="C11" s="139" t="str">
+        <x:v>커뮤니티 상태 전이, 주간/월간 랭킹, 결제 상세, 튜토리얼 slide, 관리자 추천 목록을 end-to-end smoke test로 확인한다.</x:v>
+      </x:c>
+      <x:c r="D11" s="139" t="str">
+        <x:v>7/15 프로젝트 일지 / 구현 변경 기록</x:v>
+      </x:c>
+      <x:c r="E11" s="139" t="str">
+        <x:v>문서 최신화 완료</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>

--- a/docs/최종 문서/e-학습터 개발 명세서.xlsx
+++ b/docs/최종 문서/e-학습터 개발 명세서.xlsx
@@ -2,18 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="Raecfa6e17fb94ec1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="R6ca9eb8592374ecf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="R61b0598558494330"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="R2c22be5e87cb4c7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="R19243cb6b6cc42be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="Ra32d138acfcc4a05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="R718c505631884416"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="Rf8ccab84bbd0418c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-12" sheetId="9" r:id="R2df6c0e3482044f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-14" sheetId="10" r:id="Rb25957083c0349a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-15" sheetId="11" r:id="Rc9cd09e05c6f4277"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-16" sheetId="12" r:id="Ra220a86402904975"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="R1d1e6881d77e4570"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="R5682218ee2814c91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="Rdad9fbd43ac4426e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="R7d4421e648374883"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="R88c6f3c3df2643d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="R3052805d235848c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="R5f55fa56c2c44164"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="Rbd1a885f0bde4b98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-12" sheetId="9" r:id="R021a4a6e4c984b71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-14" sheetId="10" r:id="Rf1952b81d5884be9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-15" sheetId="11" r:id="Rc060c56641d7485d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-16" sheetId="12" r:id="Rfb1fdacd391d462b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-19" sheetId="13" r:id="Rb5373d271f604435"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -24,7 +25,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="37">
+  <x:fonts count="39">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -222,8 +223,20 @@
       <x:color rgb="FF1E6570"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF145C63"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF155B63"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="38">
+  <x:fills count="42">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -410,8 +423,28 @@
         <x:fgColor rgb="FFE1F2F2"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF178A8A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE3F5F5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF1FAFA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="12">
+  <x:borders count="13">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -567,12 +600,26 @@
         <x:color rgb="FFC7E0E3"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC9E3E3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFC9E3E3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFC9E3E3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFC9E3E3"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="175">
+  <x:cellXfs count="190">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -1017,6 +1064,51 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="38" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="38" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="38" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="39" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="37" fillId="39" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="37" fillId="39" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="38" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="38" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="40" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="38" fillId="40" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="38" fillId="40" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="41" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="41" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -5977,6 +6069,197 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="72" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="38" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="179" t="str">
+        <x:v>2026.07.19 구현 최신화</x:v>
+      </x:c>
+      <x:c r="B1" s="179"/>
+      <x:c r="C1" s="179"/>
+      <x:c r="D1" s="179"/>
+      <x:c r="E1" s="179"/>
+    </x:row>
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="182" t="str">
+        <x:v>기준: 2026-07-19 local source commit f960d76, local merge commit 15a7b7e 및 내부 QA 산출물 정리 358a47a. 요구사항·DB·REST 계약 변경 없이 학습 로드맵 Nuvi 연출과 문서 정합성을 최신화.</x:v>
+      </x:c>
+      <x:c r="B2" s="182"/>
+      <x:c r="C2" s="182"/>
+      <x:c r="D2" s="182"/>
+      <x:c r="E2" s="182"/>
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="184" t="str">
+        <x:v>분류</x:v>
+      </x:c>
+      <x:c r="B3" s="184" t="str">
+        <x:v>범위</x:v>
+      </x:c>
+      <x:c r="C3" s="184" t="str">
+        <x:v>구현 기준</x:v>
+      </x:c>
+      <x:c r="D3" s="184" t="str">
+        <x:v>대표 route / source</x:v>
+      </x:c>
+      <x:c r="E3" s="184" t="str">
+        <x:v>DB / 상태</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="62" customHeight="1">
+      <x:c r="A4" s="187" t="str">
+        <x:v>학습</x:v>
+      </x:c>
+      <x:c r="B4" s="187" t="str">
+        <x:v>Nuvi 이동·첫 행성 진입 연출</x:v>
+      </x:c>
+      <x:c r="C4" s="189" t="str">
+        <x:v>방향별 cruise sprite와 pose sprite로 이동·도착 리액션을 구현한다. 현재 레벨 완료 행성이 0개이고 첫 행성을 시작하지 않았을 때만 portal/light 진입 연출을 보인다. 레벨 테스트로 열린 하위 레벨은 실제 학습 전이면 표시하고, 이미 학습한 레벨은 제외한다.</x:v>
+      </x:c>
+      <x:c r="D4" s="189" t="str">
+        <x:v>GET /learning, LearningController#dashboard, learning/main.html, learning-nuvi.js, learning.css</x:v>
+      </x:c>
+      <x:c r="E4" s="189" t="str">
+        <x:v>view-only roadmapEntryWelcome · DB/REST 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="62" customHeight="1">
+      <x:c r="A5" s="187" t="str">
+        <x:v>정적 asset</x:v>
+      </x:c>
+      <x:c r="B5" s="187" t="str">
+        <x:v>Nuvi sprite 4종</x:v>
+      </x:c>
+      <x:c r="C5" s="189" t="str">
+        <x:v>nuvi-cruise-left/right, nuvi-pose-left/right PNG를 방향·상태별 asset으로 제공한다.</x:v>
+      </x:c>
+      <x:c r="D5" s="189" t="str">
+        <x:v>static/assets/images/characters/nuvi-*.png</x:v>
+      </x:c>
+      <x:c r="E5" s="189" t="str">
+        <x:v>정적 파일 교체 · persistence 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="62" customHeight="1">
+      <x:c r="A6" s="187" t="str">
+        <x:v>MVC / 데이터</x:v>
+      </x:c>
+      <x:c r="B6" s="187" t="str">
+        <x:v>화면 전용 model</x:v>
+      </x:c>
+      <x:c r="C6" s="189" t="str">
+        <x:v>Controller가 roadmapEntryWelcome을 view model로 전달하고 template data attribute와 client JS가 진입·이동 연출을 시작한다.</x:v>
+      </x:c>
+      <x:c r="D6" s="189" t="str">
+        <x:v>LearningController, learning/main.html</x:v>
+      </x:c>
+      <x:c r="E6" s="189" t="str">
+        <x:v>기존 GET /learning 유지 · request/response DTO 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="62" customHeight="1">
+      <x:c r="A7" s="187" t="str">
+        <x:v>문서 정합성</x:v>
+      </x:c>
+      <x:c r="B7" s="187" t="str">
+        <x:v>Notion / local docs</x:v>
+      </x:c>
+      <x:c r="C7" s="189" t="str">
+        <x:v>화면 설계 v2.2, MVC v2.6, 매핑표 v0.19, 변경 기록, 추적표 v2.1, 7/19 일지와 이 시트를 동일 구현 기준으로 연결한다.</x:v>
+      </x:c>
+      <x:c r="D7" s="189" t="str">
+        <x:v>Notion direct fetch/update, 이 시트</x:v>
+      </x:c>
+      <x:c r="E7" s="189" t="str">
+        <x:v>SRS·요구사항·DB 명세·REST·DDL·sample data·ERD 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="62" customHeight="1">
+      <x:c r="A8" s="187" t="str">
+        <x:v>내부 QA</x:v>
+      </x:c>
+      <x:c r="B8" s="187" t="str">
+        <x:v>임시 산출물 정리</x:v>
+      </x:c>
+      <x:c r="C8" s="189" t="str">
+        <x:v>.sisyphus screenshot/log/evidence 파일을 정리했다. runtime source와 서비스 동작은 영향 없다.</x:v>
+      </x:c>
+      <x:c r="D8" s="189" t="str">
+        <x:v>local commit 358a47a</x:v>
+      </x:c>
+      <x:c r="E8" s="189" t="str">
+        <x:v>서비스 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="62" customHeight="1">
+      <x:c r="A9" s="187" t="str">
+        <x:v>검증</x:v>
+      </x:c>
+      <x:c r="B9" s="187" t="str">
+        <x:v>문서·코드 근거</x:v>
+      </x:c>
+      <x:c r="C9" s="189" t="str">
+        <x:v>target-date source/merge/cleanup commit, LearningController·template·정적 asset, Notion direct fetch를 대조했다.</x:v>
+      </x:c>
+      <x:c r="D9" s="189" t="str">
+        <x:v>git log 2026-07-19, git show, Notion fetch</x:v>
+      </x:c>
+      <x:c r="E9" s="189" t="str">
+        <x:v>GitHub PR 상세 metadata 미확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="62" customHeight="1">
+      <x:c r="A10" s="187" t="str">
+        <x:v>변경 제외</x:v>
+      </x:c>
+      <x:c r="B10" s="187" t="str">
+        <x:v>계약·schema</x:v>
+      </x:c>
+      <x:c r="C10" s="189" t="str">
+        <x:v>SRS·요구사항, DB 명세, REST API, DDL, sample data, ERD는 7/19 구현과 함께 변경되지 않았다.</x:v>
+      </x:c>
+      <x:c r="D10" s="189" t="str">
+        <x:v>target-date git diff</x:v>
+      </x:c>
+      <x:c r="E10" s="189" t="str">
+        <x:v>변경 없음 확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="62" customHeight="1">
+      <x:c r="A11" s="187" t="str">
+        <x:v>다음 액션</x:v>
+      </x:c>
+      <x:c r="B11" s="187" t="str">
+        <x:v>browser visual smoke test</x:v>
+      </x:c>
+      <x:c r="C11" s="189" t="str">
+        <x:v>Nuvi 이동·첫 행성 진입 연출의 시각 동작과 reduced-motion 동작을 실제 화면에서 확인한다.</x:v>
+      </x:c>
+      <x:c r="D11" s="189" t="str">
+        <x:v>learning UI</x:v>
+      </x:c>
+      <x:c r="E11" s="189" t="str">
+        <x:v>문서 반영 완료; visual QA 별도</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>

--- a/docs/최종 문서/e-학습터 개발 명세서.xlsx
+++ b/docs/최종 문서/e-학습터 개발 명세서.xlsx
@@ -2,19 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="R1d1e6881d77e4570"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="R5682218ee2814c91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="Rdad9fbd43ac4426e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="R7d4421e648374883"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="R88c6f3c3df2643d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="R3052805d235848c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="R5f55fa56c2c44164"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="Rbd1a885f0bde4b98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-12" sheetId="9" r:id="R021a4a6e4c984b71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-14" sheetId="10" r:id="Rf1952b81d5884be9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-15" sheetId="11" r:id="Rc060c56641d7485d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-16" sheetId="12" r:id="Rfb1fdacd391d462b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-19" sheetId="13" r:id="Rb5373d271f604435"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="R8824a61e3b18409e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="R0617dde6cf3f4d4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="R949bf96faf5c49dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="Reb563b7180a24caa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="R2c0af120f2d940d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="R5ba69450d375474b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="R5397364a32b84423"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="Re9ec5138d0c54b3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-12" sheetId="9" r:id="R00223e03190a4c7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-14" sheetId="10" r:id="R78412cf02b6d48bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-15" sheetId="11" r:id="Re7a42f61984e4957"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-16" sheetId="12" r:id="R267a49b513564795"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-19" sheetId="13" r:id="R49cfff49c3d143ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-20" sheetId="14" r:id="R97dc618a73b14a4b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1728,10 +1729,8 @@
           <x:t xml:space="preserve">WebMvcConfig.java / MyBatisConfig.java / FileUploadConfig.java</x:t>
         </x:is>
       </x:c>
-      <x:c r="E7" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HandlerInterceptor, MyBatis mapper scan, multipart 업로드 제한 설정</x:t>
-        </x:is>
+      <x:c r="E7" s="170" t="str">
+        <x:v>HandlerInterceptor 등록: 로그인 필요 경로, /admin/** 및 /api/admin/** 관리자 guard, MyBatis mapper scan, multipart 업로드 제한 설정</x:v>
       </x:c>
       <x:c r="F7" s="170" t="inlineStr">
         <x:is>
@@ -1763,10 +1762,8 @@
           <x:t xml:space="preserve">공통: 이현겸</x:t>
         </x:is>
       </x:c>
-      <x:c r="L7" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L7" s="170" t="str">
+        <x:v>7/20 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
@@ -1786,10 +1783,8 @@
           <x:t xml:space="preserve">SessionUser.java / LoginRequiredInterceptor.java / AdminRequiredInterceptor.java</x:t>
         </x:is>
       </x:c>
-      <x:c r="E8" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HttpSession 기반 로그인 사용자 주입, USER/ADMIN/OWNER guard 처리</x:t>
-        </x:is>
+      <x:c r="E8" s="170" t="str">
+        <x:v>HttpSession 기반 로그인 사용자 주입과 USER/ADMIN/OWNER guard 처리. AdminRequiredInterceptor는 /admin/**와 /api/admin/**를 함께 보호</x:v>
       </x:c>
       <x:c r="F8" s="170" t="inlineStr">
         <x:is>
@@ -1821,10 +1816,8 @@
           <x:t xml:space="preserve">공통: 이현겸</x:t>
         </x:is>
       </x:c>
-      <x:c r="L8" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L8" s="170" t="str">
+        <x:v>7/20 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="6" customFormat="1" ht="15" customHeight="1">
@@ -2002,10 +1995,8 @@
           <x:t xml:space="preserve">AuthController.java</x:t>
         </x:is>
       </x:c>
-      <x:c r="E13" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GET/POST /login, GET/POST /signup, POST /logout 처리. form validation, session 생성/폐기</x:t>
-        </x:is>
+      <x:c r="E13" s="170" t="str">
+        <x:v>GET/POST /login, GET/POST /signup, POST /logout 처리. 튜토리얼 마지막은 /login으로 이동하고, 로그인에서 /welcome 복귀를 제공한다. 회원가입은 이메일 폼만 제공</x:v>
       </x:c>
       <x:c r="F13" s="170" t="inlineStr">
         <x:is>
@@ -2037,10 +2028,8 @@
           <x:t xml:space="preserve">1번 이정하</x:t>
         </x:is>
       </x:c>
-      <x:c r="L13" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L13" s="170" t="str">
+        <x:v>7/20 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
@@ -2061,7 +2050,7 @@
         </x:is>
       </x:c>
       <x:c r="E14" s="170" t="str">
-        <x:v>GET /oauth/{provider}, /oauth/{provider}/callback 처리. Google/GitHub OAuth browser redirect route가 canonical</x:v>
+        <x:v>GET /oauth/{provider}, /oauth/{provider}/callback 처리. Google/GitHub OAuth browser redirect route가 canonical이며 provider redirect 환경변수가 비어 있으면 APP_BASE_URL callback 경로를 사용</x:v>
       </x:c>
       <x:c r="F14" s="170" t="inlineStr">
         <x:is>
@@ -2093,10 +2082,8 @@
           <x:t xml:space="preserve">1번 이정하</x:t>
         </x:is>
       </x:c>
-      <x:c r="L14" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L14" s="170" t="str">
+        <x:v>7/20 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
@@ -2111,15 +2098,11 @@
           <x:t xml:space="preserve">com.acorn.elearning.auth.service</x:t>
         </x:is>
       </x:c>
-      <x:c r="D15" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AuthService.java / OAuthService.java / SessionService.java</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E15" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">회원가입/login/social login/connect transaction과 OAuth state 검증</x:t>
-        </x:is>
+      <x:c r="D15" s="170" t="str">
+        <x:v>AuthService.java / OAuthService.java / SessionService.java / PasswordResetService.java / PasswordResetMailService.java</x:v>
+      </x:c>
+      <x:c r="E15" s="170" t="str">
+        <x:v>회원가입/login/social login/connect transaction, OAuth state 검증, 비밀번호 재설정 token·메일 전송을 처리한다. 미가입 이메일은 AUTH_USER_NOT_FOUND 오류로 구분한다</x:v>
       </x:c>
       <x:c r="F15" s="170" t="inlineStr">
         <x:is>
@@ -2151,10 +2134,8 @@
           <x:t xml:space="preserve">1번 이정하</x:t>
         </x:is>
       </x:c>
-      <x:c r="L15" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L15" s="170" t="str">
+        <x:v>7/20 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
@@ -2207,10 +2188,8 @@
           <x:t xml:space="preserve">1번 이정하</x:t>
         </x:is>
       </x:c>
-      <x:c r="L16" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L16" s="170" t="str">
+        <x:v>7/20 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
@@ -2231,7 +2210,7 @@
         </x:is>
       </x:c>
       <x:c r="E17" s="170" t="str">
-        <x:v>users, user_credentials, social_accounts CRUD. users.email은 중복 허용 연락처이며 login_email/nickname/provider 식별 검증은 인증 수단별로 분리</x:v>
+        <x:v>로그인·회원가입·소셜 CTA 화면. Google/GitHub CTA와 웰컴 복귀는 로그인 화면에만 두고, 회원가입 화면은 이메일 입력만 제공한다. 실패 시 same view + BindingResult 유지</x:v>
       </x:c>
       <x:c r="F17" s="170" t="inlineStr">
         <x:is>
@@ -2263,10 +2242,8 @@
           <x:t xml:space="preserve">1번 이정하</x:t>
         </x:is>
       </x:c>
-      <x:c r="L17" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L17" s="170" t="str">
+        <x:v>7/20 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" customHeight="1">
@@ -4913,7 +4890,7 @@
         </x:is>
       </x:c>
       <x:c r="E70" s="170" t="str">
-        <x:v>통계, 과목/커리큘럼/lesson/problem/user detail/community/report/notice 관리와 admin_operation_logs 기록</x:v>
+        <x:v>GET /admin/**와 관리자 상태 변경/action route를 처리한다. 사용자 상세, 공지 목록/CRUD를 포함하며, 관리자 JSON API는 WebMvcConfig의 ROLE_ADMIN guard를 함께 적용한다</x:v>
       </x:c>
       <x:c r="F70" s="170" t="inlineStr">
         <x:is>
@@ -4945,10 +4922,8 @@
           <x:t xml:space="preserve">7번 송주창</x:t>
         </x:is>
       </x:c>
-      <x:c r="L70" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L70" s="170" t="str">
+        <x:v>7/20 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="36" customHeight="1">
@@ -4968,10 +4943,8 @@
           <x:t xml:space="preserve">SubjectForm.java / LessonForm.java / ProblemForm.java / UserStatusForm.java / ReportHandleForm.java / NoticeForm.java</x:t>
         </x:is>
       </x:c>
-      <x:c r="E71" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">status enum, audit reason, ROLE_ADMIN validation</x:t>
-        </x:is>
+      <x:c r="E71" s="170" t="str">
+        <x:v>통계, 과목/커리큘럼/lesson/problem/user detail/community/report/notice 관리와 admin_operation_logs 기록. 신규 subject는 최대 sort order + 1을 사용한다</x:v>
       </x:c>
       <x:c r="F71" s="170" t="inlineStr">
         <x:is>
@@ -5003,10 +4976,8 @@
           <x:t xml:space="preserve">7번 송주창</x:t>
         </x:is>
       </x:c>
-      <x:c r="L71" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L71" s="170" t="str">
+        <x:v>7/20 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="24" customHeight="1">
@@ -6249,6 +6220,214 @@
       </x:c>
       <x:c r="E11" s="189" t="str">
         <x:v>문서 반영 완료; visual QA 별도</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="75" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="44" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="38" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="43" t="str">
+        <x:v>2026.07.20 구현 최신화</x:v>
+      </x:c>
+      <x:c r="B1" s="43"/>
+      <x:c r="C1" s="43"/>
+      <x:c r="D1" s="43"/>
+      <x:c r="E1" s="43"/>
+    </x:row>
+    <x:row r="2" ht="34" customHeight="1">
+      <x:c r="A2" s="43" t="str">
+        <x:v>기준: target-date source commit 80cc66a, b3ae034, b950248, 207f0b0, abbd057, bb6154b. 인증/온보딩, 관리자 권한·정렬, AI 분석 동시성 test를 문서 기준으로 동기화했으며 DB schema·DDL·sample data·ERD는 변경하지 않았다.</x:v>
+      </x:c>
+      <x:c r="B2" s="43"/>
+      <x:c r="C2" s="43"/>
+      <x:c r="D2" s="43"/>
+      <x:c r="E2" s="43"/>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="43" t="str">
+        <x:v>분류</x:v>
+      </x:c>
+      <x:c r="B3" s="43" t="str">
+        <x:v>범위</x:v>
+      </x:c>
+      <x:c r="C3" s="43" t="str">
+        <x:v>구현 기준</x:v>
+      </x:c>
+      <x:c r="D3" s="43" t="str">
+        <x:v>대표 route / source</x:v>
+      </x:c>
+      <x:c r="E3" s="43" t="str">
+        <x:v>DB / 상태</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="184.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A4" s="43" t="str">
+        <x:v>인증/온보딩</x:v>
+      </x:c>
+      <x:c r="B4" s="43" t="str">
+        <x:v>튜토리얼·로그인·회원가입</x:v>
+      </x:c>
+      <x:c r="C4" s="43" t="str">
+        <x:v>튜토리얼 마지막 시작하기는 /login으로 이동한다. 로그인 화면은 웰컴 복귀와 Google/GitHub 진입을 제공하고, 회원가입은 이메일 폼만 제공한다.</x:v>
+      </x:c>
+      <x:c r="D4" s="43" t="str">
+        <x:v>welcome-tutorial.js, welcome/index.html, auth/login.html, auth/signup.html</x:v>
+      </x:c>
+      <x:c r="E4" s="43" t="str">
+        <x:v>화면 flow 변경 · DB/REST schema 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="264" hidden="0" customHeight="1">
+      <x:c r="A5" s="43" t="str">
+        <x:v>OAuth</x:v>
+      </x:c>
+      <x:c r="B5" s="43" t="str">
+        <x:v>callback runtime URL</x:v>
+      </x:c>
+      <x:c r="C5" s="43" t="str">
+        <x:v>Google/GitHub redirect 환경변수가 비어 있으면 APP_BASE_URL 기반 callback URI를 사용한다. 운영 provider console의 callback URI는 현재 운영 base URL과 일치해야 한다.</x:v>
+      </x:c>
+      <x:c r="D5" s="43" t="str">
+        <x:v>application.properties, OAuthController</x:v>
+      </x:c>
+      <x:c r="E5" s="43" t="str">
+        <x:v>runtime env / provider 설정 · secret 값 문서화 금지</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="211.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A6" s="43" t="str">
+        <x:v>비밀번호 재설정</x:v>
+      </x:c>
+      <x:c r="B6" s="43" t="str">
+        <x:v>가입 상태별 응답</x:v>
+      </x:c>
+      <x:c r="C6" s="43" t="str">
+        <x:v>이메일 자격증명 계정은 reset token·mail link를 사용한다. 미가입 이메일은 AUTH_USER_NOT_FOUND 오류, 소셜 전용 계정은 별도 안내를 유지한다.</x:v>
+      </x:c>
+      <x:c r="D6" s="43" t="str">
+        <x:v>PasswordResetService, PasswordResetServiceTest</x:v>
+      </x:c>
+      <x:c r="E6" s="43" t="str">
+        <x:v>기존 password reset token schema 사용 · DDL 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="184.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A7" s="43" t="str">
+        <x:v>관리자 권한</x:v>
+      </x:c>
+      <x:c r="B7" s="43" t="str">
+        <x:v>MVC / JSON API guard</x:v>
+      </x:c>
+      <x:c r="C7" s="43" t="str">
+        <x:v>AdminRequiredInterceptor를 /admin/**와 /api/admin/**에 함께 등록한다. API endpoint request/response 계약은 유지한다.</x:v>
+      </x:c>
+      <x:c r="D7" s="43" t="str">
+        <x:v>WebMvcConfig, AdminRequiredInterceptor</x:v>
+      </x:c>
+      <x:c r="E7" s="43" t="str">
+        <x:v>접근 경계 보강 · DB 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="237.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A8" s="43" t="str">
+        <x:v>관리자 콘텐츠</x:v>
+      </x:c>
+      <x:c r="B8" s="43" t="str">
+        <x:v>목록 order / subject 생성</x:v>
+      </x:c>
+      <x:c r="C8" s="43" t="str">
+        <x:v>커리큘럼·lesson·문제 목록은 과목 sort order, Bronze→Silver→Gold, node·lesson sort order 기준으로 정렬한다. 신규 subject는 최대 sort order + 1을 사용한다.</x:v>
+      </x:c>
+      <x:c r="D8" s="43" t="str">
+        <x:v>AdminCurriculumNodeMapper, AdminLessonMapper, AdminProblemMapper, AdminContentService</x:v>
+      </x:c>
+      <x:c r="E8" s="43" t="str">
+        <x:v>조회 SQL·service 로직 변경 · schema 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A9" s="43" t="str">
+        <x:v>AI 분석</x:v>
+      </x:c>
+      <x:c r="B9" s="43" t="str">
+        <x:v>동시성 idempotency test</x:v>
+      </x:c>
+      <x:c r="C9" s="43" t="str">
+        <x:v>동시 요청의 즉시 응답은 PENDING일 수 있음을 허용하되, 최종적으로 SUCCESS report가 하나 이상 생성돼야 한다.</x:v>
+      </x:c>
+      <x:c r="D9" s="43" t="str">
+        <x:v>AiAnalysisServiceIdempotencyTest</x:v>
+      </x:c>
+      <x:c r="E9" s="43" t="str">
+        <x:v>test/CI 안정화 · 서비스 API 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="158.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A10" s="43" t="str">
+        <x:v>관리자 log</x:v>
+      </x:c>
+      <x:c r="B10" s="43" t="str">
+        <x:v>unused update path 제거</x:v>
+      </x:c>
+      <x:c r="C10" s="43" t="str">
+        <x:v>사용하지 않는 AdminOperationLog update service/mapper SQL을 제거해 중복 SET 구문 가능성을 없앴다.</x:v>
+      </x:c>
+      <x:c r="D10" s="43" t="str">
+        <x:v>AdminLogService, AdminOperationLogMapper</x:v>
+      </x:c>
+      <x:c r="E10" s="43" t="str">
+        <x:v>사용하지 않는 경로 제거 · DB 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="224.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A11" s="43" t="str">
+        <x:v>문서·검증</x:v>
+      </x:c>
+      <x:c r="B11" s="43" t="str">
+        <x:v>Notion / local sync</x:v>
+      </x:c>
+      <x:c r="C11" s="43" t="str">
+        <x:v>요구사항 v2.1, SRS v1.1, 화면 설계 v2.3, REST v2.6, MVC v2.7, 매핑표 v0.20, 추적표 v2.2, 구현 변경 기록과 7/20 일지를 연결했다. ./gradlew test가 성공했다.</x:v>
+      </x:c>
+      <x:c r="D11" s="43" t="str">
+        <x:v>git log/show, Notion direct fetch/update, ./gradlew test</x:v>
+      </x:c>
+      <x:c r="E11" s="43" t="str">
+        <x:v>GitHub PR 상세 metadata는 CLI 미인증으로 미확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="132" hidden="0" customHeight="1">
+      <x:c r="A12" s="43" t="str">
+        <x:v>변경 제외</x:v>
+      </x:c>
+      <x:c r="B12" s="43" t="str">
+        <x:v>DB 산출물</x:v>
+      </x:c>
+      <x:c r="C12" s="43" t="str">
+        <x:v>DB 명세·DDL·sample data·ERD는 target-date source diff에 변경이 없어 유지한다.</x:v>
+      </x:c>
+      <x:c r="D12" s="43" t="str">
+        <x:v>git diff --stat / target-date commits</x:v>
+      </x:c>
+      <x:c r="E12" s="43" t="str">
+        <x:v>변경 없음 확인</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9843,10 +10022,8 @@
           <x:t xml:space="preserve">ADMIN001Response 또는 관련 Page/Detail Response</x:t>
         </x:is>
       </x:c>
-      <x:c r="I63" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REST API v1.6 Error / Rule 참조</x:t>
-        </x:is>
+      <x:c r="I63" s="174" t="str">
+        <x:v>ROLE_ADMIN session guard: WebMvcConfig가 /api/admin/**에 AdminRequiredInterceptor를 적용. endpoint request/response schema 변경 없음</x:v>
       </x:c>
       <x:c r="J63" s="174" t="inlineStr">
         <x:is>
@@ -9858,10 +10035,8 @@
           <x:t xml:space="preserve">7번 송주창</x:t>
         </x:is>
       </x:c>
-      <x:c r="L63" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REST v1.6 반영</x:t>
-        </x:is>
+      <x:c r="L63" s="174" t="str">
+        <x:v>7/20 guard 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="24" customHeight="1">
@@ -9894,7 +10069,7 @@
         <x:v>ADMIN010Response 또는 관련 Detail Response</x:v>
       </x:c>
       <x:c r="I64" s="174" t="str">
-        <x:v>ROLE_ADMIN guard; 상태 변경은 audit rule 적용</x:v>
+        <x:v>ROLE_ADMIN session guard: WebMvcConfig가 /api/admin/**에 AdminRequiredInterceptor를 적용. endpoint request/response schema 변경 없음</x:v>
       </x:c>
       <x:c r="J64" s="174" t="inlineStr">
         <x:is>
@@ -9907,7 +10082,7 @@
         </x:is>
       </x:c>
       <x:c r="L64" s="174" t="str">
-        <x:v>REST v2.5 반영</x:v>
+        <x:v>7/20 guard 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="24" customHeight="1">
@@ -9947,10 +10122,8 @@
           <x:t xml:space="preserve">ADMIN020Response 또는 관련 Page/Detail Response</x:t>
         </x:is>
       </x:c>
-      <x:c r="I65" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REST API v1.6 Error / Rule 참조</x:t>
-        </x:is>
+      <x:c r="I65" s="174" t="str">
+        <x:v>ROLE_ADMIN session guard: WebMvcConfig가 /api/admin/**에 AdminRequiredInterceptor를 적용. endpoint request/response schema 변경 없음</x:v>
       </x:c>
       <x:c r="J65" s="174" t="inlineStr">
         <x:is>
@@ -9962,10 +10135,8 @@
           <x:t xml:space="preserve">7번 송주창</x:t>
         </x:is>
       </x:c>
-      <x:c r="L65" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REST v1.6 반영</x:t>
-        </x:is>
+      <x:c r="L65" s="174" t="str">
+        <x:v>7/20 guard 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="36" customHeight="1">
@@ -10005,10 +10176,8 @@
           <x:t xml:space="preserve">ADMIN030Response 또는 관련 Page/Detail Response</x:t>
         </x:is>
       </x:c>
-      <x:c r="I66" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REST API v1.6 Error / Rule 참조</x:t>
-        </x:is>
+      <x:c r="I66" s="174" t="str">
+        <x:v>ROLE_ADMIN session guard: WebMvcConfig가 /api/admin/**에 AdminRequiredInterceptor를 적용. endpoint request/response schema 변경 없음</x:v>
       </x:c>
       <x:c r="J66" s="174" t="inlineStr">
         <x:is>
@@ -10020,10 +10189,8 @@
           <x:t xml:space="preserve">7번 송주창</x:t>
         </x:is>
       </x:c>
-      <x:c r="L66" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REST v1.6 반영</x:t>
-        </x:is>
+      <x:c r="L66" s="174" t="str">
+        <x:v>7/20 guard 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="24" customHeight="1">
@@ -10063,10 +10230,8 @@
           <x:t xml:space="preserve">ADMIN040Response 또는 관련 Page/Detail Response</x:t>
         </x:is>
       </x:c>
-      <x:c r="I67" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REST API v1.6 Error / Rule 참조</x:t>
-        </x:is>
+      <x:c r="I67" s="174" t="str">
+        <x:v>ROLE_ADMIN session guard: WebMvcConfig가 /api/admin/**에 AdminRequiredInterceptor를 적용. endpoint request/response schema 변경 없음</x:v>
       </x:c>
       <x:c r="J67" s="174" t="inlineStr">
         <x:is>
@@ -10078,10 +10243,8 @@
           <x:t xml:space="preserve">7번 송주창</x:t>
         </x:is>
       </x:c>
-      <x:c r="L67" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REST v1.6 반영</x:t>
-        </x:is>
+      <x:c r="L67" s="174" t="str">
+        <x:v>7/20 guard 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="24" customHeight="1">
@@ -10121,10 +10284,8 @@
           <x:t xml:space="preserve">ADMIN050Response 또는 관련 Page/Detail Response</x:t>
         </x:is>
       </x:c>
-      <x:c r="I68" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REST API v1.6 Error / Rule 참조</x:t>
-        </x:is>
+      <x:c r="I68" s="174" t="str">
+        <x:v>ROLE_ADMIN session guard: WebMvcConfig가 /api/admin/**에 AdminRequiredInterceptor를 적용. endpoint request/response schema 변경 없음</x:v>
       </x:c>
       <x:c r="J68" s="174" t="inlineStr">
         <x:is>
@@ -10136,10 +10297,8 @@
           <x:t xml:space="preserve">7번 송주창</x:t>
         </x:is>
       </x:c>
-      <x:c r="L68" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REST v1.6 반영</x:t>
-        </x:is>
+      <x:c r="L68" s="174" t="str">
+        <x:v>7/20 guard 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="24" customHeight="1">
@@ -10179,10 +10338,8 @@
           <x:t xml:space="preserve">ADMIN060Response 또는 관련 Page/Detail Response</x:t>
         </x:is>
       </x:c>
-      <x:c r="I69" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REST API v1.6 Error / Rule 참조</x:t>
-        </x:is>
+      <x:c r="I69" s="174" t="str">
+        <x:v>ROLE_ADMIN session guard: WebMvcConfig가 /api/admin/**에 AdminRequiredInterceptor를 적용. endpoint request/response schema 변경 없음</x:v>
       </x:c>
       <x:c r="J69" s="174" t="inlineStr">
         <x:is>
@@ -10194,10 +10351,8 @@
           <x:t xml:space="preserve">7번 송주창</x:t>
         </x:is>
       </x:c>
-      <x:c r="L69" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REST v1.6 반영</x:t>
-        </x:is>
+      <x:c r="L69" s="174" t="str">
+        <x:v>7/20 guard 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -10232,7 +10387,7 @@
         <x:v>ADMIN070Response 또는 관련 Page/Detail Response</x:v>
       </x:c>
       <x:c r="I70" s="171" t="str">
-        <x:v>ROLE_ADMIN guard; 공지 변경은 admin_operation_logs 기록</x:v>
+        <x:v>ROLE_ADMIN session guard: WebMvcConfig가 /api/admin/**에 AdminRequiredInterceptor를 적용. endpoint request/response schema 변경 없음</x:v>
       </x:c>
       <x:c r="J70" s="171" t="inlineStr">
         <x:is>
@@ -10245,7 +10400,7 @@
         </x:is>
       </x:c>
       <x:c r="L70" s="171" t="str">
-        <x:v>REST v2.5 반영</x:v>
+        <x:v>7/20 guard 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -10285,10 +10440,8 @@
           <x:t xml:space="preserve">ADMIN080Response 또는 관련 Page/Detail Response</x:t>
         </x:is>
       </x:c>
-      <x:c r="I71" s="172" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REST API v1.6 Error / Rule 참조</x:t>
-        </x:is>
+      <x:c r="I71" s="172" t="str">
+        <x:v>ROLE_ADMIN session guard: WebMvcConfig가 /api/admin/**에 AdminRequiredInterceptor를 적용. endpoint request/response schema 변경 없음</x:v>
       </x:c>
       <x:c r="J71" s="172" t="inlineStr">
         <x:is>
@@ -10300,10 +10453,8 @@
           <x:t xml:space="preserve">7번 송주창</x:t>
         </x:is>
       </x:c>
-      <x:c r="L71" s="172" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REST v1.6 반영</x:t>
-        </x:is>
+      <x:c r="L71" s="172" t="str">
+        <x:v>7/20 guard 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="72">

--- a/docs/최종 문서/e-학습터 개발 명세서.xlsx
+++ b/docs/최종 문서/e-학습터 개발 명세서.xlsx
@@ -2,20 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="R8824a61e3b18409e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="R0617dde6cf3f4d4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="R949bf96faf5c49dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="Reb563b7180a24caa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="R2c0af120f2d940d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="R5ba69450d375474b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="R5397364a32b84423"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="Re9ec5138d0c54b3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-12" sheetId="9" r:id="R00223e03190a4c7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-14" sheetId="10" r:id="R78412cf02b6d48bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-15" sheetId="11" r:id="Re7a42f61984e4957"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-16" sheetId="12" r:id="R267a49b513564795"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-19" sheetId="13" r:id="R49cfff49c3d143ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-20" sheetId="14" r:id="R97dc618a73b14a4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="Rbc850c75193a42b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="R3602235986a14d4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="R91b447a9fd38414a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="Rece9d05e5b0b4eaf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="Rafcd1032ff3541a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="Re940826d90b6483b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="Rf38df282642743ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="R7cc4b56074b94a74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-12" sheetId="9" r:id="R08f4ec51bf9d49f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-14" sheetId="10" r:id="R5983fe9212624711"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-15" sheetId="11" r:id="R8208d6c727b34d26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-16" sheetId="12" r:id="Rb6dca7f9403841ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-19" sheetId="13" r:id="R0536e40706594019"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-20" sheetId="14" r:id="R6350b77fde8a41b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-21" sheetId="16" r:id="R7a3e14e98cc34f35"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1187,6 +1188,19 @@
 </x:styleSheet>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Latest20260721Table" displayName="Latest20260721Table" ref="A3:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="5">
+    <x:tableColumn id="1" name="분류"/>
+    <x:tableColumn id="2" name="범위"/>
+    <x:tableColumn id="3" name="구현 기준"/>
+    <x:tableColumn id="4" name="대표 route / source"/>
+    <x:tableColumn id="5" name="DB / 상태"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
@@ -3008,7 +3022,7 @@
         <x:v>PracticeService.java / ProblemService.java / WrongAnswerService.java / ScoreService.java / FreeCodingService.java</x:v>
       </x:c>
       <x:c r="E33" s="170" t="str">
-        <x:v>10문제 세트 생성/채점, 7/10 통과, wrong_answers queue, +5 retry bonus, score_events 기록. FreeCodingService는 로그인 학습자의 Java 17 source·stdin 실행 결과만 반환하며 DB에 저장하지 않음</x:v>
+        <x:v>10문제 세트 생성/채점, 7/10 통과, wrong_answers queue, +5 retry bonus, score_events 기록. set attempt 소유자·IN_PROGRESS 상태·전체 답안을 확인한 뒤 COMPLETED로 전환하며, 최초 score event만 출석·unlock·ranking 후속 흐름을 실행. FreeCodingService는 로그인 학습자의 Java 17 source·stdin 실행 결과만 반환하며 DB에 저장하지 않음</x:v>
       </x:c>
       <x:c r="F33" s="170" t="inlineStr">
         <x:is>
@@ -3040,10 +3054,8 @@
           <x:t xml:space="preserve">3번 고지연</x:t>
         </x:is>
       </x:c>
-      <x:c r="L33" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L33" s="170" t="str">
+        <x:v>7/21 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="36" customHeight="1">
@@ -3251,10 +3263,8 @@
           <x:t xml:space="preserve">ExamController.java</x:t>
         </x:is>
       </x:c>
-      <x:c r="E38" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GET /exams/coding-test, POST /exams, answer save, submit, retry execution, result route 처리</x:t>
-        </x:is>
+      <x:c r="E38" s="170" t="str">
+        <x:v>GET /exams/coding-test, POST /exams, 답안 저장·문제별 제출·최종 제출·재응시·결과 route 처리. 소유자 session의 검증된 전체 solutionCode만 magicSolutionCode model로 전달</x:v>
       </x:c>
       <x:c r="F38" s="170" t="inlineStr">
         <x:is>
@@ -3286,10 +3296,8 @@
           <x:t xml:space="preserve">4번 이현겸</x:t>
         </x:is>
       </x:c>
-      <x:c r="L38" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L38" s="170" t="str">
+        <x:v>7/21 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="24" customHeight="1">
@@ -3367,10 +3375,8 @@
           <x:t xml:space="preserve">AiExamService.java / TestCaseExecutionService.java / AiReviewService.java / AiAnalysisService.java / UnlockService.java</x:t>
         </x:is>
       </x:c>
-      <x:c r="E40" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ChatGPT API 문제 생성/테스트케이스 생성 보조/해설/코드 리뷰/분석 호출, 테스트케이스 실행 채점, 실패 상태 저장, retry, 2/3 통과 unlock, premium detail 접근</x:t>
-        </x:is>
+      <x:c r="E40" s="170" t="str">
+        <x:v>ChatGPT API 문제 생성/해설/코드 리뷰/분석 호출, 테스트케이스 실행 채점, 실패 상태 저장, retry, 2/3 통과 unlock, premium detail 접근. AI 생성은 prompt·solutionCode·testCases를 정규화하고 solutionCode 실행 통과 결과만 저장하며 유효하지 않으면 최대 2회 재시도</x:v>
       </x:c>
       <x:c r="F40" s="170" t="inlineStr">
         <x:is>
@@ -3402,10 +3408,8 @@
           <x:t xml:space="preserve">4번 이현겸</x:t>
         </x:is>
       </x:c>
-      <x:c r="L40" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L40" s="170" t="str">
+        <x:v>7/21 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="48" customHeight="1">
@@ -3541,10 +3545,8 @@
           <x:t xml:space="preserve">coding-test.html / result.html / index.html</x:t>
         </x:is>
       </x:c>
-      <x:c r="E43" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AI 코딩테스트 응시/결과, AI 분석 free summary/premium detail/status 화면</x:t>
-        </x:is>
+      <x:c r="E43" s="170" t="str">
+        <x:v>AI 코딩테스트 응시/결과, AI 분석 free summary/premium detail/status 화면. 실행 테스트는 case별 console output을 표시하고 해당 browser session에서 1회 이상 실행한 뒤 문제별 제출을 활성화하며, 마법 버튼은 검증된 solutionCode를 복사</x:v>
       </x:c>
       <x:c r="F43" s="170" t="inlineStr">
         <x:is>
@@ -3576,10 +3578,8 @@
           <x:t xml:space="preserve">4번 이현겸</x:t>
         </x:is>
       </x:c>
-      <x:c r="L43" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L43" s="170" t="str">
+        <x:v>7/21 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="44" s="6" customFormat="1" ht="15" customHeight="1">
@@ -3674,7 +3674,7 @@
         </x:is>
       </x:c>
       <x:c r="E46" s="170" t="str">
-        <x:v>post+attachment transaction, Markdown 본문 인라인 이미지, 1단계 대댓글, counter update, duplicate like/scrap/report guard. 게시글 수정 뒤 미참조 인라인 이미지는 attachment metadata와 저장 파일을 함께 정리</x:v>
+        <x:v>post+attachment transaction, Markdown 본문 인라인 이미지, 1단계 대댓글, counter update, duplicate like/scrap/report guard. 게시글 writer·subject를 검증하고 수정 뒤 미참조 인라인 이미지는 attachment metadata와 저장 파일을 함께 정리</x:v>
       </x:c>
       <x:c r="F46" s="170" t="inlineStr">
         <x:is>
@@ -3706,10 +3706,8 @@
           <x:t xml:space="preserve">5번 장윤성</x:t>
         </x:is>
       </x:c>
-      <x:c r="L46" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L46" s="170" t="str">
+        <x:v>7/21 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="24" customHeight="1">
@@ -3977,10 +3975,8 @@
           <x:t xml:space="preserve">DummyPaymentService.java / PremiumGrantService.java / PaymentAccessService.java</x:t>
         </x:is>
       </x:c>
-      <x:c r="E52" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">실제 PG 없이 dummy_payments 저장 후 premium_grants lifetime grant 발급</x:t>
-        </x:is>
+      <x:c r="E52" s="170" t="str">
+        <x:v>실제 PG 없이 dummy_payments 저장 후 premium_grants lifetime grant 발급. 동일 사용자·상품의 PENDING 결제는 재사용하고 ACTIVE Premium grant가 있으면 신규 결제·grant를 차단하며 user·payment·grant 조회는 transaction row lock으로 보호</x:v>
       </x:c>
       <x:c r="F52" s="170" t="inlineStr">
         <x:is>
@@ -4012,10 +4008,8 @@
           <x:t xml:space="preserve">6번 박세인</x:t>
         </x:is>
       </x:c>
-      <x:c r="L52" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L52" s="170" t="str">
+        <x:v>7/21 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="36" customHeight="1">
@@ -4534,7 +4528,7 @@
         </x:is>
       </x:c>
       <x:c r="E63" s="170" t="str">
-        <x:v>GET /ranking. scopeType/scopeKey/periodType/gradeCode filter와 로그인 사용자의 current league code를 기준으로 ranking 화면 제공</x:v>
+        <x:v>GET /ranking. active subject tab을 동적으로 제공하며 subject 선택이 없으면 전체 월간, 있으면 과목별 주간 랭킹 화면을 제공. current league·grade filter 없음</x:v>
       </x:c>
       <x:c r="F63" s="170" t="inlineStr">
         <x:is>
@@ -4566,10 +4560,8 @@
           <x:t xml:space="preserve">3번 고지연</x:t>
         </x:is>
       </x:c>
-      <x:c r="L63" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L63" s="170" t="str">
+        <x:v>7/21 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" customHeight="1">
@@ -4590,7 +4582,7 @@
         </x:is>
       </x:c>
       <x:c r="E64" s="170" t="str">
-        <x:v>score_events 기반 ranking_scores 조회. 출석/연속 학습은 점수 산정에서 제외하고, 선택한 통합/과목 범위의 현재 league 내 rankNo를 다시 계산</x:v>
+        <x:v>score_events 기반 ranking_scores 조회. 출석/연속 학습은 점수 산정에서 제외하고, 전체는 월간 SUBJECT score 합계, 과목은 주간 SUBJECT score로 rankNo를 계산</x:v>
       </x:c>
       <x:c r="F64" s="170" t="inlineStr">
         <x:is>
@@ -4622,10 +4614,8 @@
           <x:t xml:space="preserve">3번 고지연</x:t>
         </x:is>
       </x:c>
-      <x:c r="L64" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L64" s="170" t="str">
+        <x:v>7/21 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="36" customHeight="1">
@@ -4646,7 +4636,7 @@
         </x:is>
       </x:c>
       <x:c r="E65" s="170" t="str">
-        <x:v>랭킹 검색 조건, current league tab, 내 랭킹 응답 DTO</x:v>
+        <x:v>랭킹 검색 조건, active subject tab, 전체/과목 기간 기준 내 랭킹·점수 구성 응답 DTO. current league DTO와 filter는 사용하지 않음</x:v>
       </x:c>
       <x:c r="F65" s="170" t="inlineStr">
         <x:is>
@@ -4678,10 +4668,8 @@
           <x:t xml:space="preserve">3번 고지연</x:t>
         </x:is>
       </x:c>
-      <x:c r="L65" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L65" s="170" t="str">
+        <x:v>7/21 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="24" customHeight="1">
@@ -4702,7 +4690,7 @@
         </x:is>
       </x:c>
       <x:c r="E66" s="170" t="str">
-        <x:v>ranking_scores, score_events 조회. current league code와 선택 scope에 맞춰 rankNo를 산정</x:v>
+        <x:v>ranking_scores, score_events 조회. current league 없이 전체 월간 SUBJECT score 합계 또는 과목별 주간 SUBJECT score 기준으로 rankNo를 산정</x:v>
       </x:c>
       <x:c r="F66" s="170" t="inlineStr">
         <x:is>
@@ -4734,10 +4722,8 @@
           <x:t xml:space="preserve">3번 고지연</x:t>
         </x:is>
       </x:c>
-      <x:c r="L66" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L66" s="170" t="str">
+        <x:v>7/21 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" customHeight="1">
@@ -4758,7 +4744,7 @@
         </x:is>
       </x:c>
       <x:c r="E67" s="170" t="str">
-        <x:v>랭킹 목록과 통합/과목·기간·현재 league filter 화면</x:v>
+        <x:v>랭킹 목록과 active subject tab, 전체 월간/과목별 주간 filter 화면. current league filter 없음</x:v>
       </x:c>
       <x:c r="F67" s="170" t="inlineStr">
         <x:is>
@@ -4790,10 +4776,8 @@
           <x:t xml:space="preserve">3번 고지연</x:t>
         </x:is>
       </x:c>
-      <x:c r="L67" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L67" s="170" t="str">
+        <x:v>7/21 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="68" s="6" customFormat="1" ht="15" customHeight="1">
@@ -4834,7 +4818,7 @@
         <x:v>AdminController.java / AdminApiController.java / AdminStatsController.java / AdminContentController.java / AdminUserController.java / AdminCommunityController.java / AdminReportController.java / AdminNoticeController.java</x:v>
       </x:c>
       <x:c r="E69" s="170" t="str">
-        <x:v>GET /admin/** 및 관리자 상태 변경/action route 처리. 사용자 상세, 공지 목록/CRUD를 포함하며 ROLE_ADMIN guard 필수</x:v>
+        <x:v>GET /admin/** 및 관리자 상태 변경/action route 처리. 사용자 상세, 공지 목록/CRUD를 포함하며 ROLE_ADMIN guard 필수. 자기 자신과 마지막 활성 관리자의 상태 변경을 차단</x:v>
       </x:c>
       <x:c r="F69" s="170" t="inlineStr">
         <x:is>
@@ -4866,10 +4850,8 @@
           <x:t xml:space="preserve">7번 송주창</x:t>
         </x:is>
       </x:c>
-      <x:c r="L69" s="170" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 기준 반영</x:t>
-        </x:is>
+      <x:c r="L69" s="170" t="str">
+        <x:v>7/21 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="72" customHeight="1">
@@ -4890,7 +4872,7 @@
         </x:is>
       </x:c>
       <x:c r="E70" s="170" t="str">
-        <x:v>GET /admin/**와 관리자 상태 변경/action route를 처리한다. 사용자 상세, 공지 목록/CRUD를 포함하며, 관리자 JSON API는 WebMvcConfig의 ROLE_ADMIN guard를 함께 적용한다</x:v>
+        <x:v>GET /admin/**와 관리자 상태 변경/action route를 처리한다. 사용자 상세, 공지 목록/CRUD를 포함하며, 관리자 JSON API는 WebMvcConfig의 ROLE_ADMIN guard를 함께 적용한다. self·last active admin guard를 transaction에서 검증</x:v>
       </x:c>
       <x:c r="F70" s="170" t="inlineStr">
         <x:is>
@@ -4923,7 +4905,7 @@
         </x:is>
       </x:c>
       <x:c r="L70" s="170" t="str">
-        <x:v>7/20 구현 반영</x:v>
+        <x:v>7/21 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="36" customHeight="1">
@@ -5133,10 +5115,8 @@
           <x:t xml:space="preserve">ExamController.java</x:t>
         </x:is>
       </x:c>
-      <x:c r="E75" s="172" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">한 화면에 한 문제씩 응시하며 제출 시 답안 저장 후 다음 문제로 이동. 모든 문제 제출 후 최종 제출 팝업을 거쳐 결과 화면 이동</x:t>
-        </x:is>
+      <x:c r="E75" s="172" t="str">
+        <x:v>한 화면에 한 문제씩 응시하며 실행 테스트를 1회 이상 완료한 뒤 제출할 수 있다. 제출 시 답안 저장 후 다음 문제로 이동하고, 모든 문제 제출 후 최종 제출 팝업을 거쳐 결과 화면으로 이동. 마법 버튼은 검증된 전체 solutionCode 복사</x:v>
       </x:c>
       <x:c r="F75" s="172" t="inlineStr">
         <x:is>
@@ -5168,10 +5148,8 @@
           <x:t xml:space="preserve">4번 이현겸</x:t>
         </x:is>
       </x:c>
-      <x:c r="L75" s="172" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">구현 변경 반영</x:t>
-        </x:is>
+      <x:c r="L75" s="172" t="str">
+        <x:v>7/21 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -5191,10 +5169,8 @@
           <x:t xml:space="preserve">ExamApiController.java</x:t>
         </x:is>
       </x:c>
-      <x:c r="E76" s="172" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">문제 단위 조회, 답안 저장, 실행 테스트, 최종 제출, 상태/결과 조회 API 제공</x:t>
-        </x:is>
+      <x:c r="E76" s="172" t="str">
+        <x:v>문제 단위 조회, 답안 저장, 실행 테스트, 최종 제출, 상태/결과 조회 API 제공. 실행 테스트는 case별 actualOutput과 통과 결과를 반환하며 답안을 저장하지 않음</x:v>
       </x:c>
       <x:c r="F76" s="172" t="inlineStr">
         <x:is>
@@ -5226,10 +5202,8 @@
           <x:t xml:space="preserve">4번 이현겸</x:t>
         </x:is>
       </x:c>
-      <x:c r="L76" s="172" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">구현 변경 반영</x:t>
-        </x:is>
+      <x:c r="L76" s="172" t="str">
+        <x:v>7/21 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -5249,10 +5223,8 @@
           <x:t xml:space="preserve">CodeMirror local bundle / code-runner.js</x:t>
         </x:is>
       </x:c>
-      <x:c r="E77" s="172" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">코드 에디터는 로컬 번들로 제공하고, 에디터 로드 완료 전까지 로딩 모달을 유지. 실행 테스트 결과는 시험 화면에 표시</x:t>
-        </x:is>
+      <x:c r="E77" s="172" t="str">
+        <x:v>코드 에디터는 로컬 번들로 제공하고, 에디터 로드 완료 전까지 로딩 모달을 유지. 실행 테스트 결과는 case별 console output으로 표시하며 sessionStorage 실행 이력으로 제출 gate를 제어</x:v>
       </x:c>
       <x:c r="F77" s="172" t="inlineStr">
         <x:is>
@@ -5284,10 +5256,8 @@
           <x:t xml:space="preserve">4번 이현겸</x:t>
         </x:is>
       </x:c>
-      <x:c r="L77" s="172" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">구현 변경 반영</x:t>
-        </x:is>
+      <x:c r="L77" s="172" t="str">
+        <x:v>7/21 구현 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -6439,6 +6409,217 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="58" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="36" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="43" t="str">
+        <x:v>2026.07.21 구현 최신화</x:v>
+      </x:c>
+      <x:c r="B1" s="43" t="str"/>
+      <x:c r="C1" s="43" t="str"/>
+      <x:c r="D1" s="43" t="str"/>
+      <x:c r="E1" s="43" t="str"/>
+    </x:row>
+    <x:row r="2" ht="40" customHeight="1">
+      <x:c r="A2" s="43" t="str">
+        <x:v>기준: 7/21 source commits, 요구사항 v2.2 → SRS v1.2 → DB v2.4(구조 유지) → REST v2.7 → MVC v2.8 → 매핑표 v0.21. DDL·ERD 변경 없음, 시연 셋업 v2.5.5·ranking seed는 운영 데이터 변경.</x:v>
+      </x:c>
+      <x:c r="B2" s="43" t="str"/>
+      <x:c r="C2" s="43" t="str"/>
+      <x:c r="D2" s="43" t="str"/>
+      <x:c r="E2" s="43" t="str"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="43" t="str">
+        <x:v>분류</x:v>
+      </x:c>
+      <x:c r="B3" s="43" t="str">
+        <x:v>범위</x:v>
+      </x:c>
+      <x:c r="C3" s="43" t="str">
+        <x:v>구현 기준</x:v>
+      </x:c>
+      <x:c r="D3" s="43" t="str">
+        <x:v>대표 route / source</x:v>
+      </x:c>
+      <x:c r="E3" s="43" t="str">
+        <x:v>DB / 상태</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="58" customHeight="1">
+      <x:c r="A4" s="43" t="str">
+        <x:v>AI 코딩테스트</x:v>
+      </x:c>
+      <x:c r="B4" s="43" t="str">
+        <x:v>생성 검증·실행 test·마법 버튼</x:v>
+      </x:c>
+      <x:c r="C4" s="43" t="str">
+        <x:v>prompt·solutionCode·testCases와 solutionCode 실행을 검증하고 최대 2회 재시도. case별 console output을 표시하며 실행 1회 후 제출 활성화. 마법 버튼은 검증된 전체 solutionCode만 복사</x:v>
+      </x:c>
+      <x:c r="D4" s="43" t="str">
+        <x:v>ExamController, AiExamService, AiGeneratedProblemParser, code-runner.js</x:v>
+      </x:c>
+      <x:c r="E4" s="43" t="str">
+        <x:v>exam_sessions, ai_exam_problems, exam_answers, ai_request_logs / 7/21 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="58" customHeight="1">
+      <x:c r="A5" s="43" t="str">
+        <x:v>일반 문제풀이</x:v>
+      </x:c>
+      <x:c r="B5" s="43" t="str">
+        <x:v>완료 멱등성</x:v>
+      </x:c>
+      <x:c r="C5" s="43" t="str">
+        <x:v>owner·IN_PROGRESS·전체 답안 제출을 확인한 뒤 COMPLETED 전환. 최초 score event만 출석·unlock·ranking 후속 처리를 실행</x:v>
+      </x:c>
+      <x:c r="D5" s="43" t="str">
+        <x:v>PracticeService, PracticeApiController</x:v>
+      </x:c>
+      <x:c r="E5" s="43" t="str">
+        <x:v>practice_set_attempts, practice_submissions, score_events / 7/21 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="58" customHeight="1">
+      <x:c r="A6" s="43" t="str">
+        <x:v>결제/Premium</x:v>
+      </x:c>
+      <x:c r="B6" s="43" t="str">
+        <x:v>중복 결제·grant 차단</x:v>
+      </x:c>
+      <x:c r="C6" s="43" t="str">
+        <x:v>동일 사용자·상품의 PENDING 결제 재사용, ACTIVE Premium grant가 있으면 신규 결제·grant 차단. transaction row lock 적용</x:v>
+      </x:c>
+      <x:c r="D6" s="43" t="str">
+        <x:v>DummyPaymentService, PremiumGrantService</x:v>
+      </x:c>
+      <x:c r="E6" s="43" t="str">
+        <x:v>dummy_payments, premium_grants / 7/21 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="58" customHeight="1">
+      <x:c r="A7" s="43" t="str">
+        <x:v>관리자</x:v>
+      </x:c>
+      <x:c r="B7" s="43" t="str">
+        <x:v>사용자 상태 보호</x:v>
+      </x:c>
+      <x:c r="C7" s="43" t="str">
+        <x:v>자기 자신의 상태와 마지막 활성 관리자 1명의 비활성·탈퇴 상태 변경을 차단</x:v>
+      </x:c>
+      <x:c r="D7" s="43" t="str">
+        <x:v>AdminUserService, AdminApiController</x:v>
+      </x:c>
+      <x:c r="E7" s="43" t="str">
+        <x:v>users, admin_operation_logs / 7/21 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="58" customHeight="1">
+      <x:c r="A8" s="43" t="str">
+        <x:v>랭킹</x:v>
+      </x:c>
+      <x:c r="B8" s="43" t="str">
+        <x:v>전체/과목 집계</x:v>
+      </x:c>
+      <x:c r="C8" s="43" t="str">
+        <x:v>current league·grade filter를 제거. active subject tab, 전체 월간 SUBJECT score 합계, 과목별 주간 SUBJECT score 기준</x:v>
+      </x:c>
+      <x:c r="D8" s="43" t="str">
+        <x:v>RankingController, RankingService, RankingScoreMapper</x:v>
+      </x:c>
+      <x:c r="E8" s="43" t="str">
+        <x:v>ranking_scores, score_events, subjects / 7/21 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="58" customHeight="1">
+      <x:c r="A9" s="43" t="str">
+        <x:v>커뮤니티</x:v>
+      </x:c>
+      <x:c r="B9" s="43" t="str">
+        <x:v>게시글/첨부 경계</x:v>
+      </x:c>
+      <x:c r="C9" s="43" t="str">
+        <x:v>게시글 writer·subject와 attachment post ownership을 검증하고 미참조 인라인 image metadata·저장 파일을 정리</x:v>
+      </x:c>
+      <x:c r="D9" s="43" t="str">
+        <x:v>PostService, AttachmentService</x:v>
+      </x:c>
+      <x:c r="E9" s="43" t="str">
+        <x:v>community_posts, post_attachments / 7/21 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="58" customHeight="1">
+      <x:c r="A10" s="43" t="str">
+        <x:v>시연 데이터</x:v>
+      </x:c>
+      <x:c r="B10" s="43" t="str">
+        <x:v>셋업·랭킹 seed</x:v>
+      </x:c>
+      <x:c r="C10" s="43" t="str">
+        <x:v>DB schema·DDL·ERD는 유지. Knowva_demo_setup_data v2.5.5와 ranking seed를 시연 운영 데이터로 반영</x:v>
+      </x:c>
+      <x:c r="D10" s="43" t="str">
+        <x:v>docs/ddl/Knowva_demo_setup_data.sql, ranking_seed_data.sql</x:v>
+      </x:c>
+      <x:c r="E10" s="43" t="str">
+        <x:v>seed 운영 변경 / schema 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="58" customHeight="1">
+      <x:c r="A11" s="43" t="str">
+        <x:v>문서 정합성</x:v>
+      </x:c>
+      <x:c r="B11" s="43" t="str">
+        <x:v>Notion·Excel</x:v>
+      </x:c>
+      <x:c r="C11" s="43" t="str">
+        <x:v>요구사항 v2.2, SRS v1.2, 화면 설계 v2.4, REST v2.7, MVC v2.8, 매핑 v0.21, 구현 기록·추적표·일지를 같은 근거로 연결</x:v>
+      </x:c>
+      <x:c r="D11" s="43" t="str">
+        <x:v>Notion 개발 명세 / 프로젝트 일지 7/21</x:v>
+      </x:c>
+      <x:c r="E11" s="43" t="str">
+        <x:v>최종 Excel 본문·최신화 시트 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="58" customHeight="1">
+      <x:c r="A12" s="43" t="str">
+        <x:v>검증</x:v>
+      </x:c>
+      <x:c r="B12" s="43" t="str">
+        <x:v>현재 기준선</x:v>
+      </x:c>
+      <x:c r="C12" s="43" t="str">
+        <x:v>develop worktree clean, ./gradlew test 성공. 브라우저 end-to-end smoke test는 별도 확인 필요</x:v>
+      </x:c>
+      <x:c r="D12" s="43" t="str">
+        <x:v>ELearning/./gradlew test</x:v>
+      </x:c>
+      <x:c r="E12" s="43" t="str">
+        <x:v>2026-07-22 실행 확인</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd831f28b0fd4e4e"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
@@ -8153,10 +8334,8 @@
           <x:t xml:space="preserve">/api/practice/sets/{setAttemptId}/complete</x:t>
         </x:is>
       </x:c>
-      <x:c r="D30" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PRACTICE-004. 세트 완료. 7/10 통과, progress/attendance/score 처리, idempotency required</x:t>
-        </x:is>
+      <x:c r="D30" s="174" t="str">
+        <x:v>PRACTICE-004. 세트 완료. owner·IN_PROGRESS·전체 답안 제출을 검증한 뒤 COMPLETED로 전환하고, 최초 score event만 progress/attendance/unlock/ranking 후속 처리를 실행</x:v>
       </x:c>
       <x:c r="E30" s="174" t="inlineStr">
         <x:is>
@@ -8178,10 +8357,8 @@
           <x:t xml:space="preserve">PRACTICE004Response 또는 관련 Page/Detail Response</x:t>
         </x:is>
       </x:c>
-      <x:c r="I30" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">idempotency required, 공통 ErrorCode 사용</x:t>
-        </x:is>
+      <x:c r="I30" s="174" t="str">
+        <x:v>idempotency required, OWNER·IN_PROGRESS·전체 답안 검증, 중복 완료 후속 처리 차단</x:v>
       </x:c>
       <x:c r="J30" s="174" t="inlineStr">
         <x:is>
@@ -8193,10 +8370,8 @@
           <x:t xml:space="preserve">3번 고지연</x:t>
         </x:is>
       </x:c>
-      <x:c r="L30" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REST v1.6 반영</x:t>
-        </x:is>
+      <x:c r="L30" s="174" t="str">
+        <x:v>REST v2.7 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="24" customHeight="1">
@@ -8599,10 +8774,8 @@
           <x:t xml:space="preserve">/api/exams</x:t>
         </x:is>
       </x:c>
-      <x:c r="D38" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EXAM-002. ChatGPT API 기반 AI 코딩테스트 session 및 3문항 생성</x:t>
-        </x:is>
+      <x:c r="D38" s="174" t="str">
+        <x:v>EXAM-002. ChatGPT API 기반 AI 코딩테스트 session 및 3문항 생성. prompt·solutionCode·testCases를 검증하고 solutionCode 실행을 통과한 문제만 저장하며 유효하지 않으면 최대 2회 재시도</x:v>
       </x:c>
       <x:c r="E38" s="174" t="inlineStr">
         <x:is>
@@ -8624,10 +8797,8 @@
           <x:t xml:space="preserve">EXAM002Response 또는 관련 Page/Detail Response</x:t>
         </x:is>
       </x:c>
-      <x:c r="I38" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REST API v1.6 Error / Rule 참조</x:t>
-        </x:is>
+      <x:c r="I38" s="174" t="str">
+        <x:v>학습 Gate·OWNER 검증, 생성 응답 형식/실행 검증 실패 시 최대 2회 재시도 후 실패 상태·로그 기록</x:v>
       </x:c>
       <x:c r="J38" s="174" t="inlineStr">
         <x:is>
@@ -8639,10 +8810,8 @@
           <x:t xml:space="preserve">4번 이현겸</x:t>
         </x:is>
       </x:c>
-      <x:c r="L38" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REST v1.6 반영</x:t>
-        </x:is>
+      <x:c r="L38" s="174" t="str">
+        <x:v>REST v2.7 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="24" customHeight="1">
@@ -9300,7 +9469,7 @@
         </x:is>
       </x:c>
       <x:c r="D50" s="174" t="str">
-        <x:v>COM-002. 게시글 작성/수정/삭제. Markdown 본문을 저장하며 multipart 작성은 idempotency required, 수정 뒤 미참조 인라인 이미지는 정리, 삭제는 soft delete</x:v>
+        <x:v>COM-002. 게시글 작성/수정/삭제. Markdown 본문을 저장하며 multipart 작성은 idempotency required, writer·subject 검증, 수정 뒤 미참조 인라인 이미지는 정리, 삭제는 soft delete</x:v>
       </x:c>
       <x:c r="E50" s="174" t="inlineStr">
         <x:is>
@@ -9330,7 +9499,7 @@
         </x:is>
       </x:c>
       <x:c r="L50" s="174" t="str">
-        <x:v>REST v2.5 반영</x:v>
+        <x:v>REST v2.7 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="24" customHeight="1">
@@ -9346,7 +9515,7 @@
         </x:is>
       </x:c>
       <x:c r="D51" s="174" t="str">
-        <x:v>COM-003. 별도 첨부 추가/삭제. 파일 크기/확장자/MIME 검증. 본문 인라인 이미지는 COM-003A route를 사용</x:v>
+        <x:v>COM-003. 별도 첨부 추가/삭제. 파일 크기/확장자/MIME·post ownership 검증. 본문 인라인 이미지는 COM-003A route를 사용하고 미참조 file lifecycle을 정리</x:v>
       </x:c>
       <x:c r="E51" s="174" t="inlineStr">
         <x:is>
@@ -9378,7 +9547,7 @@
         </x:is>
       </x:c>
       <x:c r="L51" s="174" t="str">
-        <x:v>REST v2.5 반영</x:v>
+        <x:v>REST v2.7 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="24" customHeight="1">
@@ -9723,10 +9892,8 @@
           <x:t xml:space="preserve">/api/payments/dummy</x:t>
         </x:is>
       </x:c>
-      <x:c r="D58" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PAY-002. dummy payment 성공 처리. premium_grants lifetime grant 발급, idempotency required</x:t>
-        </x:is>
+      <x:c r="D58" s="174" t="str">
+        <x:v>PAY-002. dummy payment 성공 처리. 동일 사용자·상품의 PENDING 결제는 재사용하고 ACTIVE premium_grants가 있으면 신규 결제·lifetime grant 발급을 차단</x:v>
       </x:c>
       <x:c r="E58" s="174" t="inlineStr">
         <x:is>
@@ -9748,10 +9915,8 @@
           <x:t xml:space="preserve">PAY002Response 또는 관련 Page/Detail Response</x:t>
         </x:is>
       </x:c>
-      <x:c r="I58" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">idempotency required, 공통 ErrorCode 사용</x:t>
-        </x:is>
+      <x:c r="I58" s="174" t="str">
+        <x:v>idempotency required, user·payment·grant transaction row lock, ACTIVE grant 중복 차단</x:v>
       </x:c>
       <x:c r="J58" s="174" t="inlineStr">
         <x:is>
@@ -9763,10 +9928,8 @@
           <x:t xml:space="preserve">6번 박세인</x:t>
         </x:is>
       </x:c>
-      <x:c r="L58" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REST v1.6 반영</x:t>
-        </x:is>
+      <x:c r="L58" s="174" t="str">
+        <x:v>REST v2.7 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="24" customHeight="1">
@@ -9844,7 +10007,7 @@
         </x:is>
       </x:c>
       <x:c r="D60" s="174" t="str">
-        <x:v>RANK-001. scopeType/scopeKey/periodType/gradeCode/page와 로그인 사용자의 current league 기준 랭킹 조회</x:v>
+        <x:v>RANK-001. subjectId가 없으면 전체 월간, 있으면 과목별 주간 랭킹 조회. current league·grade filter 없음</x:v>
       </x:c>
       <x:c r="E60" s="174" t="inlineStr">
         <x:is>
@@ -9857,16 +10020,16 @@
         </x:is>
       </x:c>
       <x:c r="G60" s="174" t="str">
-        <x:v>query: scopeType, scopeKey, periodType, gradeCode, page</x:v>
+        <x:v>query: subjectId?, periodType?, page, size; subjectId가 없으면 MONTHLY, 있으면 WEEKLY</x:v>
       </x:c>
       <x:c r="H60" s="174" t="str">
-        <x:v>RankingPageResponse { currentLeagueCode, leagueTabs, items[] }</x:v>
+        <x:v>RankingPageResponse { subjectTabs, selectedSubjectId, top3, rankingList, mySummary, scoreBreakdown, periodType }</x:v>
       </x:c>
       <x:c r="I60" s="174" t="str">
-        <x:v>로그인 필요; 출석·streak 점수 제외</x:v>
+        <x:v>로그인 필요; 리그·grade filter 없음; 출석·streak 점수 제외</x:v>
       </x:c>
       <x:c r="J60" s="174" t="str">
-        <x:v>ranking_scores, score_events; 선택 통합/과목 범위에서 current league 내 rankNo 재계산</x:v>
+        <x:v>ranking_scores, score_events; 전체 월간 SUBJECT score 합계 또는 과목별 주간 SUBJECT score</x:v>
       </x:c>
       <x:c r="K60" s="174" t="inlineStr">
         <x:is>
@@ -9874,7 +10037,7 @@
         </x:is>
       </x:c>
       <x:c r="L60" s="174" t="str">
-        <x:v>REST v2.5 반영</x:v>
+        <x:v>REST v2.7 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="24" customHeight="1">
@@ -9890,7 +10053,7 @@
         </x:is>
       </x:c>
       <x:c r="D61" s="174" t="str">
-        <x:v>RANK-002. 선택 범위와 current league 기준 내 랭킹 조회</x:v>
+        <x:v>RANK-002. subjectId가 없으면 전체 월간, 있으면 과목별 주간 내 랭킹·점수 구성 조회. current league filter 없음</x:v>
       </x:c>
       <x:c r="E61" s="174" t="inlineStr">
         <x:is>
@@ -9903,16 +10066,16 @@
         </x:is>
       </x:c>
       <x:c r="G61" s="174" t="str">
-        <x:v>query: scopeType, scopeKey, periodType, gradeCode</x:v>
+        <x:v>query: subjectId?, periodType?; subjectId가 없으면 MONTHLY, 있으면 WEEKLY</x:v>
       </x:c>
       <x:c r="H61" s="174" t="str">
-        <x:v>MyRankingResponse { currentLeagueCode, rankNo, score }</x:v>
+        <x:v>MyRankingResponse { selectedSubjectId, periodType, mySummary, scoreBreakdown }</x:v>
       </x:c>
       <x:c r="I61" s="174" t="str">
-        <x:v>로그인 필요; 선택 scope의 current league 기준</x:v>
+        <x:v>로그인 필요; 리그·grade filter 없음</x:v>
       </x:c>
       <x:c r="J61" s="174" t="str">
-        <x:v>ranking_scores, score_events; current league 내 rankNo 반환</x:v>
+        <x:v>ranking_scores, score_events; 전체/과목 기간 기준 집계</x:v>
       </x:c>
       <x:c r="K61" s="174" t="inlineStr">
         <x:is>
@@ -9920,7 +10083,7 @@
         </x:is>
       </x:c>
       <x:c r="L61" s="174" t="str">
-        <x:v>REST v2.5 반영</x:v>
+        <x:v>REST v2.7 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="24" customHeight="1">
@@ -10050,7 +10213,7 @@
         <x:v>/api/admin/users, /api/admin/users/{userId}/detail, /api/admin/users/{userId}/status</x:v>
       </x:c>
       <x:c r="D64" s="174" t="str">
-        <x:v>ADMIN-010. 사용자 목록/상세/상태 변경. premium은 role이 아니라 grant 관리</x:v>
+        <x:v>ADMIN-010. 사용자 목록/상세/상태 변경. premium은 role이 아니라 grant 관리. 관리자는 자기 자신과 마지막 활성 관리자의 상태를 변경할 수 없음</x:v>
       </x:c>
       <x:c r="E64" s="174" t="inlineStr">
         <x:is>
@@ -10069,7 +10232,7 @@
         <x:v>ADMIN010Response 또는 관련 Detail Response</x:v>
       </x:c>
       <x:c r="I64" s="174" t="str">
-        <x:v>ROLE_ADMIN session guard: WebMvcConfig가 /api/admin/**에 AdminRequiredInterceptor를 적용. endpoint request/response schema 변경 없음</x:v>
+        <x:v>ROLE_ADMIN session guard; self·last active admin 상태 변경 차단</x:v>
       </x:c>
       <x:c r="J64" s="174" t="inlineStr">
         <x:is>
@@ -10082,7 +10245,7 @@
         </x:is>
       </x:c>
       <x:c r="L64" s="174" t="str">
-        <x:v>7/20 guard 반영</x:v>
+        <x:v>REST v2.7 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="24" customHeight="1">
@@ -10607,10 +10770,8 @@
           <x:t xml:space="preserve">/api/exams/{examId}/problems/{problemNo}/answers/{aiProblemId}/test-run</x:t>
         </x:is>
       </x:c>
-      <x:c r="D75" s="172" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">최종 제출 전 실행 테스트 수행. 화면에 실행 시간과 테스트 결과 표시</x:t>
-        </x:is>
+      <x:c r="D75" s="172" t="str">
+        <x:v>EXAM-004B. 최종 제출 전 실행 테스트 수행. 화면에 case별 console output·실행 시간·통과 여부를 표시하고, 해당 browser session에서 실행 완료 후 문제별 제출을 활성화</x:v>
       </x:c>
       <x:c r="E75" s="172" t="inlineStr">
         <x:is>
@@ -10627,15 +10788,11 @@
           <x:t xml:space="preserve">path + body: answerText</x:t>
         </x:is>
       </x:c>
-      <x:c r="H75" s="172" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ExamCodeRunResponse</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I75" s="172" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">OWNER guard, compile/runtime error 처리</x:t>
-        </x:is>
+      <x:c r="H75" s="172" t="str">
+        <x:v>ExamCodeRunResponse { cases:[{actualOutput, passed, message}], executionTimeMs }</x:v>
+      </x:c>
+      <x:c r="I75" s="172" t="str">
+        <x:v>OWNER guard, compile/runtime error 처리, 실행 테스트는 답안 저장이 아님</x:v>
       </x:c>
       <x:c r="J75" s="172" t="inlineStr">
         <x:is>
@@ -10647,10 +10804,8 @@
           <x:t xml:space="preserve">4번 이현겸</x:t>
         </x:is>
       </x:c>
-      <x:c r="L75" s="172" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REST v1.6 반영</x:t>
-        </x:is>
+      <x:c r="L75" s="172" t="str">
+        <x:v>REST v2.7 반영</x:v>
       </x:c>
     </x:row>
     <x:row r="76">

--- a/docs/최종 문서/e-학습터 개발 명세서.xlsx
+++ b/docs/최종 문서/e-학습터 개발 명세서.xlsx
@@ -2,21 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="Rbc850c75193a42b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="R3602235986a14d4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="R91b447a9fd38414a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="Rece9d05e5b0b4eaf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="Rafcd1032ff3541a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="Re940826d90b6483b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="Rf38df282642743ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="R7cc4b56074b94a74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-12" sheetId="9" r:id="R08f4ec51bf9d49f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-14" sheetId="10" r:id="R5983fe9212624711"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-15" sheetId="11" r:id="R8208d6c727b34d26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-16" sheetId="12" r:id="Rb6dca7f9403841ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-19" sheetId="13" r:id="R0536e40706594019"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-20" sheetId="14" r:id="R6350b77fde8a41b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-21" sheetId="16" r:id="R7a3e14e98cc34f35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="Reac7c249d7c34e5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="Ra4c7623860eb421f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="R8c3a853a61b647ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="R9109ace612eb448a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="R28a8d4e488974b71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="R06bcfb2da0654fcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="Rfcafd57e12454363"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="Rb02bde4705c84fcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-12" sheetId="9" r:id="R8b7a19a0b1e84f66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-14" sheetId="10" r:id="Rc26e93a749184ee0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-15" sheetId="11" r:id="R76a2d3090059479c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-16" sheetId="12" r:id="R563e22ae4aa1420f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-19" sheetId="13" r:id="Re44327b9aa6942ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-20" sheetId="14" r:id="Raa0d725da76d4b5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-21" sheetId="16" r:id="R86f7c5fb7cb14c25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-22" sheetId="17" r:id="R01ad53c7333340d6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -238,7 +239,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="42">
+  <x:fills count="44">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -445,8 +446,18 @@
         <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF006B8F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFB9E1F2"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="13">
+  <x:borders count="14">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -616,12 +627,26 @@
         <x:color rgb="FFC9E3E3"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF72C7E6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF72C7E6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF72C7E6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF72C7E6"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="190">
+  <x:cellXfs count="197">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -1110,6 +1135,27 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="24" fillId="41" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="42" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="43" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -6615,8 +6661,216 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd831f28b0fd4e4e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd755a5a702e5482e"/>
   </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="58" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="36" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="175" t="str">
+        <x:v>2026.07.22 구현 최신화</x:v>
+      </x:c>
+      <x:c r="B1" s="175"/>
+      <x:c r="C1" s="175"/>
+      <x:c r="D1" s="175"/>
+      <x:c r="E1" s="175"/>
+    </x:row>
+    <x:row r="2" ht="40" customHeight="1">
+      <x:c r="A2" s="175" t="str">
+        <x:v>기준: 7/22 source ed60ffb·07011ea·f8add78·672ae92·15fe03e·91f1f7f. 요구사항 v2.2 → SRS v1.2 → DB v2.4(구조 유지) → REST v2.8 → MVC v2.9 → 매핑표 v0.22. DDL·sample·ERD 변경 없음, demo setup v2.5.6은 랭킹 fixture 통합.</x:v>
+      </x:c>
+      <x:c r="B2" s="175"/>
+      <x:c r="C2" s="175"/>
+      <x:c r="D2" s="175"/>
+      <x:c r="E2" s="175"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="194" t="str">
+        <x:v>분류</x:v>
+      </x:c>
+      <x:c r="B3" s="194" t="str">
+        <x:v>범위</x:v>
+      </x:c>
+      <x:c r="C3" s="194" t="str">
+        <x:v>구현 기준</x:v>
+      </x:c>
+      <x:c r="D3" s="194" t="str">
+        <x:v>대표 route / source</x:v>
+      </x:c>
+      <x:c r="E3" s="194" t="str">
+        <x:v>DB / 상태</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="58" customHeight="1">
+      <x:c r="A4" s="195" t="str">
+        <x:v>인증/세션</x:v>
+      </x:c>
+      <x:c r="B4" s="195" t="str">
+        <x:v>로그아웃·remember-me 정리</x:v>
+      </x:c>
+      <x:c r="C4" s="195" t="str">
+        <x:v>custom 로그아웃은 session invalidate와 remember-me cookie 삭제를 함께 처리하고, POST form은 CSRF token을 포함한다. session Premium은 실제 active grant로 계산</x:v>
+      </x:c>
+      <x:c r="D4" s="195" t="str">
+        <x:v>AuthController, AuthApiController, AuthService, WebSecurityConfig</x:v>
+      </x:c>
+      <x:c r="E4" s="195" t="str">
+        <x:v>users, user_settings, premium_grants / schema 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="58" customHeight="1">
+      <x:c r="A5" s="196" t="str">
+        <x:v>사용자/Premium</x:v>
+      </x:c>
+      <x:c r="B5" s="196" t="str">
+        <x:v>session 접근 상태</x:v>
+      </x:c>
+      <x:c r="C5" s="196" t="str">
+        <x:v>로그인 session model의 Premium 여부는 PaymentAccessService가 실제 active grant를 조회해 계산한다. 화면·기능 분기는 저장된 임시 flag가 아닌 현재 접근 상태를 사용</x:v>
+      </x:c>
+      <x:c r="D5" s="196" t="str">
+        <x:v>AuthService, PaymentAccessService</x:v>
+      </x:c>
+      <x:c r="E5" s="196" t="str">
+        <x:v>premium_grants 참조 / schema 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="58" customHeight="1">
+      <x:c r="A6" s="195" t="str">
+        <x:v>학습</x:v>
+      </x:c>
+      <x:c r="B6" s="195" t="str">
+        <x:v>과목 공개 범위·Nuvi 첫 진입</x:v>
+      </x:c>
+      <x:c r="C6" s="195" t="str">
+        <x:v>일반 사용자는 activeOnly=false여도 활성 과목만 조회한다. BASIC 시작 뒤 target artwork가 실제 layout된 경우에만 Nuvi run을 수행</x:v>
+      </x:c>
+      <x:c r="D6" s="195" t="str">
+        <x:v>LearningApiController, LearningController, learning-nuvi.js</x:v>
+      </x:c>
+      <x:c r="E6" s="195" t="str">
+        <x:v>subjects, user_subject_enrollments / 조회 권한·화면 보강</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="58" customHeight="1">
+      <x:c r="A7" s="196" t="str">
+        <x:v>오답 복습</x:v>
+      </x:c>
+      <x:c r="B7" s="196" t="str">
+        <x:v>비로그인 권한 guard</x:v>
+      </x:c>
+      <x:c r="C7" s="196" t="str">
+        <x:v>summary·list·소유 오답 조회는 null session user를 AUTH_REQUIRED로 처리해 NPE를 차단</x:v>
+      </x:c>
+      <x:c r="D7" s="196" t="str">
+        <x:v>WrongAnswerService, ReviewController, PracticeApiController</x:v>
+      </x:c>
+      <x:c r="E7" s="196" t="str">
+        <x:v>wrong_answers / schema 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="58" customHeight="1">
+      <x:c r="A8" s="195" t="str">
+        <x:v>커뮤니티</x:v>
+      </x:c>
+      <x:c r="B8" s="195" t="str">
+        <x:v>본문 검증·반응 중복 안정화</x:v>
+      </x:c>
+      <x:c r="C8" s="195" t="str">
+        <x:v>작성/수정 본문은 2,000자 이하. like/scrap unique 충돌은 이미 반응한 상태와 현재 count를 반환해 500·중복 증가를 방지</x:v>
+      </x:c>
+      <x:c r="D8" s="195" t="str">
+        <x:v>PostForm, CreatePostRequest, UpdatePostRequest, ReactionService</x:v>
+      </x:c>
+      <x:c r="E8" s="195" t="str">
+        <x:v>community_posts, post_likes, post_scraps / schema 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="58" customHeight="1">
+      <x:c r="A9" s="196" t="str">
+        <x:v>시연 데이터</x:v>
+      </x:c>
+      <x:c r="B9" s="196" t="str">
+        <x:v>랭킹 fixture 통합</x:v>
+      </x:c>
+      <x:c r="C9" s="196" t="str">
+        <x:v>Knowva_demo_setup_data.sql v2.5.6에 랭킹 시연 계정 20명, score event, exam session, WEEKLY·MONTHLY ranking score를 통합. 별도 ranking seed 실행 불필요</x:v>
+      </x:c>
+      <x:c r="D9" s="196" t="str">
+        <x:v>docs/ddl/Knowva_demo_setup_data.sql</x:v>
+      </x:c>
+      <x:c r="E9" s="196" t="str">
+        <x:v>seed data 변경 / DB schema 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="58" customHeight="1">
+      <x:c r="A10" s="195" t="str">
+        <x:v>발표 산출물</x:v>
+      </x:c>
+      <x:c r="B10" s="195" t="str">
+        <x:v>기능별 핵심 로직 문서</x:v>
+      </x:c>
+      <x:c r="C10" s="195" t="str">
+        <x:v>학습·랭킹·회원/인증·공통 기능의 발표용 핵심 로직 Markdown과 인증 관련 이미지 산출물을 병합</x:v>
+      </x:c>
+      <x:c r="D10" s="195" t="str">
+        <x:v>docs/산출물/*</x:v>
+      </x:c>
+      <x:c r="E10" s="195" t="str">
+        <x:v>발표 문서·이미지 추가</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="58" customHeight="1">
+      <x:c r="A11" s="196" t="str">
+        <x:v>문서 정합성</x:v>
+      </x:c>
+      <x:c r="B11" s="196" t="str">
+        <x:v>Notion·Excel·일지</x:v>
+      </x:c>
+      <x:c r="C11" s="196" t="str">
+        <x:v>REST v2.8, MVC v2.9, 화면 설계 v2.5, 매핑표 v0.22, 추적표 v2.4, 구현 변경 기록과 7/22 일지를 같은 근거로 연결</x:v>
+      </x:c>
+      <x:c r="D11" s="196" t="str">
+        <x:v>Notion 개발 명세 / 프로젝트 일지 7/22</x:v>
+      </x:c>
+      <x:c r="E11" s="196" t="str">
+        <x:v>최종 Excel 최신화 시트 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="58" customHeight="1">
+      <x:c r="A12" s="195" t="str">
+        <x:v>검증</x:v>
+      </x:c>
+      <x:c r="B12" s="195" t="str">
+        <x:v>현재 기준선</x:v>
+      </x:c>
+      <x:c r="C12" s="195" t="str">
+        <x:v>7/22 local Git log와 source diff를 대조하고, Java test suite를 실행한다. GitHub CLI는 미인증 상태여서 PR 상세 metadata는 별도 조회하지 않음</x:v>
+      </x:c>
+      <x:c r="D12" s="195" t="str">
+        <x:v>ELearning/./gradlew test</x:v>
+      </x:c>
+      <x:c r="E12" s="195" t="str">
+        <x:v>문서 반영 후 검증</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 

--- a/docs/최종 문서/e-학습터 개발 명세서.xlsx
+++ b/docs/최종 문서/e-학습터 개발 명세서.xlsx
@@ -2,22 +2,24 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="Reac7c249d7c34e5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="Ra4c7623860eb421f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="R8c3a853a61b647ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="R9109ace612eb448a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="R28a8d4e488974b71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="R06bcfb2da0654fcd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="Rfcafd57e12454363"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="Rb02bde4705c84fcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-12" sheetId="9" r:id="R8b7a19a0b1e84f66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-14" sheetId="10" r:id="Rc26e93a749184ee0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-15" sheetId="11" r:id="R76a2d3090059479c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-16" sheetId="12" r:id="R563e22ae4aa1420f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-19" sheetId="13" r:id="Re44327b9aa6942ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-20" sheetId="14" r:id="Raa0d725da76d4b5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-21" sheetId="16" r:id="R86f7c5fb7cb14c25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-22" sheetId="17" r:id="R01ad53c7333340d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="R5027dae005aa4c26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="Rd0d6e5788ad0424f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="R610452e39a994d6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="R9002ccadc029482c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="R6eaf143bc5d54dee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="Ra8391a7cf34e4afb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="R22924fe5c89b4ac6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="Rd50aadaa1db748e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-12" sheetId="9" r:id="R6e4481bd12f3438c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-14" sheetId="10" r:id="Rb73e088bb45a45c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-15" sheetId="11" r:id="R4d58c3c9e6854a6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-16" sheetId="12" r:id="R9893cd6c14724fa3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-19" sheetId="13" r:id="R2b8120336f4d4971"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-20" sheetId="14" r:id="R6b86f2efe5d444ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-21" sheetId="16" r:id="R07219eef8d7e4948"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-22" sheetId="17" r:id="R1cb345a6c3944f34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-23" sheetId="18" r:id="R504a583853114a33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-24" sheetId="19" r:id="Rca632e8c20b64561"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -28,7 +30,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="39">
+  <x:fonts count="42">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -238,8 +240,26 @@
       <x:color rgb="FF155B63"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF153B4A"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="44">
+  <x:fills count="49">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -456,6 +476,31 @@
         <x:fgColor rgb="FFB9E1F2"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF007C91"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDF4FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF007C91"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDF4FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="14">
     <x:border/>
@@ -646,7 +691,7 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="197">
+  <x:cellXfs count="221">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -1156,6 +1201,72 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="40" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="40" fillId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="40" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="48" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="48" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="40" fillId="48" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2404,7 +2515,7 @@
         </x:is>
       </x:c>
       <x:c r="E20" s="170" t="str">
-        <x:v>GET/PATCH profile/security/settings, GET /mypage, GET /settings/**, DELETE/POST withdraw 처리. 프로필 이미지가 없으면 마이페이지·커뮤니티·공통 header가 같은 기본 avatar 규칙을 사용</x:v>
+        <x:v>GET/PATCH profile/security/settings, GET /mypage, GET /settings/**, DELETE/POST withdraw 처리. 프로필 이미지가 없으면 마이페이지·커뮤니티·공통 header가 같은 기본 avatar 규칙을 사용하고, 출석 완료 날짜는 attendance_records를 근거로 누비 도장으로 시각화</x:v>
       </x:c>
       <x:c r="F20" s="170" t="inlineStr">
         <x:is>
@@ -2632,7 +2743,7 @@
         </x:is>
       </x:c>
       <x:c r="E24" s="170" t="str">
-        <x:v>설정, 소셜 연동, 결제 내역, 마이페이지 요약 화면. 업로드 프로필 이미지가 없으면 공통 header·커뮤니티와 동일한 기본 avatar를 표시</x:v>
+        <x:v>설정, 소셜 연동, 결제 내역, 마이페이지 요약·출석 달력 화면. 업로드 프로필 이미지가 없으면 공통 header·커뮤니티와 동일한 기본 avatar를 표시하고, 출석 완료 날짜에는 누비 도장을 표시</x:v>
       </x:c>
       <x:c r="F24" s="170" t="inlineStr">
         <x:is>
@@ -3016,7 +3127,7 @@
         <x:v>PracticeController.java / PracticeApiController.java / ReviewController.java</x:v>
       </x:c>
       <x:c r="E32" s="170" t="str">
-        <x:v>GET/POST /learning/practice, 답안 제출·세트 완료, GET /practice/free-coding, POST /api/practice/free-coding/run, 오답 목록/detail/retry/reviewed route 처리</x:v>
+        <x:v>GET/POST /learning/practice, 답안 제출·세트 완료, GET /practice/free-coding, POST /api/practice/free-coding/run, 오답 목록/detail/retry/reviewed, GET note.md, POST community-draft route 처리</x:v>
       </x:c>
       <x:c r="F32" s="170" t="inlineStr">
         <x:is>
@@ -3068,7 +3179,7 @@
         <x:v>PracticeService.java / ProblemService.java / WrongAnswerService.java / ScoreService.java / FreeCodingService.java</x:v>
       </x:c>
       <x:c r="E33" s="170" t="str">
-        <x:v>10문제 세트 생성/채점, 7/10 통과, wrong_answers queue, +5 retry bonus, score_events 기록. set attempt 소유자·IN_PROGRESS 상태·전체 답안을 확인한 뒤 COMPLETED로 전환하며, 최초 score event만 출석·unlock·ranking 후속 흐름을 실행. FreeCodingService는 로그인 학습자의 Java 17 source·stdin 실행 결과만 반환하며 DB에 저장하지 않음</x:v>
+        <x:v>10문제 세트 생성/채점, 7/10 통과, wrong_answers queue, +5 retry bonus, score_events 기록. set attempt 소유자·IN_PROGRESS 상태·전체 답안을 확인한 뒤 COMPLETED로 전환하며, 최초 score event만 출석·unlock·ranking 후속 흐름을 실행. WrongAnswerService는 소유 오답과 문제를 조회해 Markdown note를 생성하고 DB 저장 없이 다운로드·커뮤니티 초안에 재사용. FreeCodingService는 로그인 학습자의 Java 17 source·stdin 실행 결과만 반환하며 DB에 저장하지 않음</x:v>
       </x:c>
       <x:c r="F33" s="170" t="inlineStr">
         <x:is>
@@ -3232,7 +3343,7 @@
         <x:v>practice.html / free-coding.html / review.html / review-list.html</x:v>
       </x:c>
       <x:c r="E36" s="170" t="str">
-        <x:v>일반 문제풀이, Java 17 자유 코딩(CodeMirror local bundle·표준 입력·시스템 출력), 오답 상세·목록 화면. 자유 코딩 실행 상태는 비저장</x:v>
+        <x:v>일반 문제풀이, Java 17 자유 코딩(CodeMirror local bundle·표준 입력·시스템 출력), 오답 상세·목록 화면. 오답 상세는 Markdown 파일 저장과 커뮤니티 초안 이어쓰기를 제공하며, 자유 코딩 실행 상태는 비저장</x:v>
       </x:c>
       <x:c r="F36" s="170" t="inlineStr">
         <x:is>
@@ -3666,7 +3777,7 @@
         <x:v>CommunityController.java / PostController.java / CommunityApiController.java / CommentController.java / ReactionController.java / ReportController.java / CommunityProfileController.java</x:v>
       </x:c>
       <x:c r="E45" s="170" t="str">
-        <x:v>게시판 목록/상세/작성/수정/삭제, 댓글/좋아요/스크랩/신고 AJAX, 커뮤니티 프로필 처리. Markdown 기본 toolbar·slash command와 인라인 이미지 upload endpoint를 제공</x:v>
+        <x:v>게시판 목록/상세/작성/수정/삭제, 댓글/좋아요/스크랩/신고 AJAX, 커뮤니티 프로필 처리. Markdown 기본 toolbar·slash command와 인라인 이미지 upload endpoint를 제공하고, 오답노트 flash draft를 Markdown 작성 화면에 prefill</x:v>
       </x:c>
       <x:c r="F45" s="170" t="inlineStr">
         <x:is>
@@ -3774,7 +3885,7 @@
         </x:is>
       </x:c>
       <x:c r="E47" s="170" t="str">
-        <x:v>boardType, Markdown content/attachment policy, owner/admin validation. 커뮤니티 프로필은 전체/과목 filter와 최신·조회·인기 정렬의 오름·내림차순을 지원</x:v>
+        <x:v>boardType, Markdown content/attachment policy, owner/admin validation. 커뮤니티 본문은 최대 10,000자이며, 프로필은 전체/과목 filter와 최신·조회·인기 정렬의 오름·내림차순을 지원</x:v>
       </x:c>
       <x:c r="F47" s="170" t="inlineStr">
         <x:is>
@@ -3886,7 +3997,7 @@
         </x:is>
       </x:c>
       <x:c r="E49" s="170" t="str">
-        <x:v>커뮤니티 메인/게시판/상세/글쓰기/수정/프로필 화면. 기본 toolbar와 Markdown slash command로 본문을 작성·조회 렌더링하고, 본문 이미지를 인라인으로 표시. 프로필은 전체/과목 filter와 최신·조회·인기 정렬을 제공</x:v>
+        <x:v>커뮤니티 메인/게시판/상세/글쓰기/수정/프로필 화면. 기본 toolbar와 Markdown slash command로 본문을 작성·조회 렌더링하고, 본문 이미지를 인라인으로 표시. 오답노트 초안은 제목·과목·공부일지·본문을 채운 상태로 열리며, 프로필은 전체/과목 filter와 최신·조회·인기 정렬을 제공</x:v>
       </x:c>
       <x:c r="F49" s="170" t="inlineStr">
         <x:is>
@@ -6661,7 +6772,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd755a5a702e5482e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e728d3f0cee42f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6863,6 +6974,422 @@
       </x:c>
       <x:c r="E12" s="195" t="str">
         <x:v>문서 반영 후 검증</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="40" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="197" t="str">
+        <x:v>2026.07.23 구현 최신화</x:v>
+      </x:c>
+      <x:c r="B1" s="197"/>
+      <x:c r="C1" s="197"/>
+      <x:c r="D1" s="197"/>
+      <x:c r="E1" s="197"/>
+    </x:row>
+    <x:row r="2" ht="40" customHeight="1">
+      <x:c r="A2" s="43" t="str">
+        <x:v>기준: 7/23 target source 10d6d82·fdb7785·2972db9·b59c80f·b1bd8ca·9871c37·9673fc6·b39ace2. 요구사항 v2.2 → SRS v1.2 → DB v2.5(데이터 실행 계약) → REST v2.9 → MVC v3.0 → 화면 설계 v2.6 → 매핑표 v0.23. DB schema·DDL table 정의·ERD 변경 없음.</x:v>
+      </x:c>
+      <x:c r="B2" s="43"/>
+      <x:c r="C2" s="43"/>
+      <x:c r="D2" s="43"/>
+      <x:c r="E2" s="43"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="202" t="str">
+        <x:v>분류</x:v>
+      </x:c>
+      <x:c r="B3" s="202" t="str">
+        <x:v>범위</x:v>
+      </x:c>
+      <x:c r="C3" s="202" t="str">
+        <x:v>구현 기준</x:v>
+      </x:c>
+      <x:c r="D3" s="202" t="str">
+        <x:v>대표 route / source</x:v>
+      </x:c>
+      <x:c r="E3" s="202" t="str">
+        <x:v>DB / 상태</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="57" customHeight="1">
+      <x:c r="A4" s="206" t="str">
+        <x:v>운영/배포</x:v>
+      </x:c>
+      <x:c r="B4" s="207" t="str">
+        <x:v>CI/CD 구조</x:v>
+      </x:c>
+      <x:c r="C4" s="207" t="str">
+        <x:v>GitHub Actions는 application test·bootJar, Lambda test/build, SAM deploy, ECR push, SSM EC2 deploy를 순서대로 수행한다. OIDC 단기 credential만 사용한다.</x:v>
+      </x:c>
+      <x:c r="D4" s="207" t="str">
+        <x:v>.github/workflows/deploy.yml, infra/aws/template.yaml</x:v>
+      </x:c>
+      <x:c r="E4" s="207" t="str">
+        <x:v>DB 자동 실행 없음 / 배포 v1.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="57" customHeight="1">
+      <x:c r="A5" s="205" t="str">
+        <x:v>비밀번호 재설정</x:v>
+      </x:c>
+      <x:c r="B5" s="204" t="str">
+        <x:v>Lambda → SES</x:v>
+      </x:c>
+      <x:c r="C5" s="204" t="str">
+        <x:v>PasswordResetMailService는 MailTransport에만 의존한다. Lambda mode는 request 검증 후 SES로 발송하고 실패를 인증 mail failure로 정리한다.</x:v>
+      </x:c>
+      <x:c r="D5" s="204" t="str">
+        <x:v>PasswordResetMailService, LambdaPasswordResetMailTransport, PasswordResetMailHandler</x:v>
+      </x:c>
+      <x:c r="E5" s="204" t="str">
+        <x:v>password_reset_tokens 정책 유지 / schema 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="57" customHeight="1">
+      <x:c r="A6" s="206" t="str">
+        <x:v>커뮤니티·프로필 파일</x:v>
+      </x:c>
+      <x:c r="B6" s="207" t="str">
+        <x:v>private ObjectStorage</x:v>
+      </x:c>
+      <x:c r="C6" s="207" t="str">
+        <x:v>첨부·인라인 이미지·프로필 이미지는 key 기반 ObjectStorage local/mirror/s3 mode로 저장한다. 운영 object는 application route로만 조회한다.</x:v>
+      </x:c>
+      <x:c r="D6" s="207" t="str">
+        <x:v>AttachmentService, UserService, ObjectStorage, S3ObjectStorage</x:v>
+      </x:c>
+      <x:c r="E6" s="207" t="str">
+        <x:v>post_attachments·users metadata 유지 / schema 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="57" customHeight="1">
+      <x:c r="A7" s="205" t="str">
+        <x:v>AI 분석</x:v>
+      </x:c>
+      <x:c r="B7" s="204" t="str">
+        <x:v>자동 갱신 안정화</x:v>
+      </x:c>
+      <x:c r="C7" s="204" t="str">
+        <x:v>예기치 않은 RuntimeException도 FAILED report로 정리한다. 분석 화면은 CSRF header로 refresh 요청을 보내고 실패 시 기본 누적 분석을 유지한다.</x:v>
+      </x:c>
+      <x:c r="D7" s="204" t="str">
+        <x:v>AiAnalysisService, analysis/index.html, analysis.css</x:v>
+      </x:c>
+      <x:c r="E7" s="204" t="str">
+        <x:v>ai_analysis_reports 상태 갱신 / schema 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="57" customHeight="1">
+      <x:c r="A8" s="206" t="str">
+        <x:v>Java 커리큘럼</x:v>
+      </x:c>
+      <x:c r="B8" s="207" t="str">
+        <x:v>시연 데이터</x:v>
+      </x:c>
+      <x:c r="C8" s="207" t="str">
+        <x:v>Java 15행성·150레슨·1,500문제 data를 추가하고 Silver 마지막 레슨은 짧은 객관식·빈칸·코드 채우기로 조정했다.</x:v>
+      </x:c>
+      <x:c r="D8" s="207" t="str">
+        <x:v>docs/ddl/Knowva_Java_Curriculum_Data.sql</x:v>
+      </x:c>
+      <x:c r="E8" s="207" t="str">
+        <x:v>curriculum data 변경 / schema·ERD 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="57" customHeight="1">
+      <x:c r="A9" s="205" t="str">
+        <x:v>데이터 실행</x:v>
+      </x:c>
+      <x:c r="B9" s="204" t="str">
+        <x:v>safe update / seed 순서</x:v>
+      </x:c>
+      <x:c r="C9" s="204" t="str">
+        <x:v>clean DB 실행 순서는 DDL → demo setup → Java curriculum → community seed다. curriculum/community seed는 session SQL_SAFE_UPDATES 값을 저장·복원한다.</x:v>
+      </x:c>
+      <x:c r="D9" s="204" t="str">
+        <x:v>docs/ddl/*_Data.sql, community_post_seed_data.sql</x:v>
+      </x:c>
+      <x:c r="E9" s="204" t="str">
+        <x:v>base Knowva_sample_data.sql 실행 기준 제외</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="57" customHeight="1">
+      <x:c r="A10" s="206" t="str">
+        <x:v>화면·문서</x:v>
+      </x:c>
+      <x:c r="B10" s="207" t="str">
+        <x:v>분석/파일 경계</x:v>
+      </x:c>
+      <x:c r="C10" s="207" t="str">
+        <x:v>화면 설계·매핑표는 비차단 분석 안내와 private storage 경계를, 구현 변경 기록은 team-scope 7/23 변경을 반영한다.</x:v>
+      </x:c>
+      <x:c r="D10" s="207" t="str">
+        <x:v>Notion 화면 설계 v2.6, 매핑표 v0.23, 구현 변경 기록</x:v>
+      </x:c>
+      <x:c r="E10" s="207" t="str">
+        <x:v>요구사항·SRS 범위 유지</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="57" customHeight="1">
+      <x:c r="A11" s="205" t="str">
+        <x:v>팀 산출물</x:v>
+      </x:c>
+      <x:c r="B11" s="204" t="str">
+        <x:v>개인 문서</x:v>
+      </x:c>
+      <x:c r="C11" s="204" t="str">
+        <x:v>팀원 개인 문서 PDF 병합을 최종 산출물로 기록한다. 기능·DB schema 영향은 없다.</x:v>
+      </x:c>
+      <x:c r="D11" s="204" t="str">
+        <x:v>docs/개인 문서</x:v>
+      </x:c>
+      <x:c r="E11" s="204" t="str">
+        <x:v>문서 산출물 추가</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="57" customHeight="1">
+      <x:c r="A12" s="206" t="str">
+        <x:v>검증</x:v>
+      </x:c>
+      <x:c r="B12" s="207" t="str">
+        <x:v>근거 대조</x:v>
+      </x:c>
+      <x:c r="C12" s="207" t="str">
+        <x:v>target-date Git log·source diff·Notion direct fetch로 구현/문서를 대조한다. GitHub CLI는 미인증으로 PR 상세 metadata를 별도 조회하지 못했다.</x:v>
+      </x:c>
+      <x:c r="D12" s="207" t="str">
+        <x:v>git log, git diff, Notion fetch</x:v>
+      </x:c>
+      <x:c r="E12" s="207" t="str">
+        <x:v>문서 반영 후 재조회·workbook render 예정</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="40" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="210" t="str">
+        <x:v>2026.07.24 구현 최신화</x:v>
+      </x:c>
+      <x:c r="B1" s="210"/>
+      <x:c r="C1" s="210"/>
+      <x:c r="D1" s="210"/>
+      <x:c r="E1" s="210"/>
+    </x:row>
+    <x:row r="2" ht="40" customHeight="1">
+      <x:c r="A2" s="175" t="str">
+        <x:v>기준: 2026-07-24 local source. 출석 도장과 오답노트 다운로드·커뮤니티 초안 기능을 반영했다. 요구사항·SRS·DB schema·ERD 변경 없음.</x:v>
+      </x:c>
+      <x:c r="B2" s="175"/>
+      <x:c r="C2" s="175"/>
+      <x:c r="D2" s="175"/>
+      <x:c r="E2" s="175"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="214" t="str">
+        <x:v>분류</x:v>
+      </x:c>
+      <x:c r="B3" s="214" t="str">
+        <x:v>범위</x:v>
+      </x:c>
+      <x:c r="C3" s="214" t="str">
+        <x:v>구현 기준</x:v>
+      </x:c>
+      <x:c r="D3" s="214" t="str">
+        <x:v>대표 route / source</x:v>
+      </x:c>
+      <x:c r="E3" s="214" t="str">
+        <x:v>DB / 상태</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="57" customHeight="1">
+      <x:c r="A4" s="217" t="str">
+        <x:v>마이페이지</x:v>
+      </x:c>
+      <x:c r="B4" s="216" t="str">
+        <x:v>출석 도장 표시</x:v>
+      </x:c>
+      <x:c r="C4" s="216" t="str">
+        <x:v>저장된 attendance_records 날짜를 바꾸지 않고, 달력 cell에 Nuvi celebrate 도장을 overlay한다. reduced motion에서는 animation을 멈춘다.</x:v>
+      </x:c>
+      <x:c r="D4" s="216" t="str">
+        <x:v>mypage/index.html, mypage.css</x:v>
+      </x:c>
+      <x:c r="E4" s="216" t="str">
+        <x:v>attendance_records schema·판정 유지 / UI 변경</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="57" customHeight="1">
+      <x:c r="A5" s="220" t="str">
+        <x:v>오답 복습</x:v>
+      </x:c>
+      <x:c r="B5" s="219" t="str">
+        <x:v>Markdown 파일</x:v>
+      </x:c>
+      <x:c r="C5" s="219" t="str">
+        <x:v>소유 오답·문제를 Markdown으로 구성해 note.md UTF-8 attachment로 반환한다.</x:v>
+      </x:c>
+      <x:c r="D5" s="219" t="str">
+        <x:v>WrongAnswerService, WrongAnswerNote, ReviewController</x:v>
+      </x:c>
+      <x:c r="E5" s="219" t="str">
+        <x:v>wrong_answers·practice_problems read only / schema 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="57" customHeight="1">
+      <x:c r="A6" s="217" t="str">
+        <x:v>커뮤니티</x:v>
+      </x:c>
+      <x:c r="B6" s="216" t="str">
+        <x:v>초안 이어쓰기</x:v>
+      </x:c>
+      <x:c r="C6" s="216" t="str">
+        <x:v>POST는 게시하지 않고 flash로 제목·과목·공부일지·Markdown 본문을 작성 화면에 전달한다. 사용자가 수정 후 등록한다.</x:v>
+      </x:c>
+      <x:c r="D6" s="216" t="str">
+        <x:v>ReviewController → PostController → community/write</x:v>
+      </x:c>
+      <x:c r="E6" s="216" t="str">
+        <x:v>community_posts 기존 table / auto publish 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="57" customHeight="1">
+      <x:c r="A7" s="220" t="str">
+        <x:v>보안/입력 정책</x:v>
+      </x:c>
+      <x:c r="B7" s="219" t="str">
+        <x:v>CSRF·본문 길이</x:v>
+      </x:c>
+      <x:c r="C7" s="219" t="str">
+        <x:v>오답 상세 모든 POST form에 CSRF를 넣고, community 본문 검증을 10,000자로 통일한다.</x:v>
+      </x:c>
+      <x:c r="D7" s="219" t="str">
+        <x:v>review.html, PostForm, Create/UpdatePostRequest</x:v>
+      </x:c>
+      <x:c r="E7" s="219" t="str">
+        <x:v>MEDIUMTEXT 유지 / app policy 10,000자</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="57" customHeight="1">
+      <x:c r="A8" s="217" t="str">
+        <x:v>DDL/셋업</x:v>
+      </x:c>
+      <x:c r="B8" s="216" t="str">
+        <x:v>실행 계약</x:v>
+      </x:c>
+      <x:c r="C8" s="216" t="str">
+        <x:v>DDL header와 community_posts content metadata comment에 기존 table 기반 구현 규칙을 기록한다.</x:v>
+      </x:c>
+      <x:c r="D8" s="216" t="str">
+        <x:v>Knowva_DDL.sql, Knowva_demo_setup_data.sql v2.5.8</x:v>
+      </x:c>
+      <x:c r="E8" s="216" t="str">
+        <x:v>migration·new seed·ERD 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="57" customHeight="1">
+      <x:c r="A9" s="220" t="str">
+        <x:v>검증</x:v>
+      </x:c>
+      <x:c r="B9" s="219" t="str">
+        <x:v>service·MVC</x:v>
+      </x:c>
+      <x:c r="C9" s="219" t="str">
+        <x:v>소유권, Markdown content, attachment header, flash draft prefill을 검증했다.</x:v>
+      </x:c>
+      <x:c r="D9" s="219" t="str">
+        <x:v>WrongAnswerServiceNoteTest 등 4 tests</x:v>
+      </x:c>
+      <x:c r="E9" s="219" t="str">
+        <x:v>./gradlew test 성공</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="57" customHeight="1">
+      <x:c r="A10" s="217" t="str">
+        <x:v>PPT</x:v>
+      </x:c>
+      <x:c r="B10" s="216" t="str">
+        <x:v>기능 반영</x:v>
+      </x:c>
+      <x:c r="C10" s="216" t="str">
+        <x:v>마이페이지 출석 도장과 오답노트 다운로드→커뮤니티 초안 흐름을 발표 자료에 반영한다.</x:v>
+      </x:c>
+      <x:c r="D10" s="216" t="str">
+        <x:v>e-학습터 발표 자료_기능반영본.pptx</x:v>
+      </x:c>
+      <x:c r="E10" s="216" t="str">
+        <x:v>별도 반영본 생성</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="57" customHeight="1">
+      <x:c r="A11" s="220" t="str">
+        <x:v>미진행</x:v>
+      </x:c>
+      <x:c r="B11" s="219" t="str">
+        <x:v>7일 미접속 메일</x:v>
+      </x:c>
+      <x:c r="C11" s="219" t="str">
+        <x:v>Lambda scheduler·SES 이메일 기능은 이번 작업 범위에서 구현하지 않는다.</x:v>
+      </x:c>
+      <x:c r="D11" s="219" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E11" s="219" t="str">
+        <x:v>기획만 유지 / 코드·DDL·PPT 구조도 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="57" customHeight="1">
+      <x:c r="A12" s="217" t="str">
+        <x:v>문서 정보</x:v>
+      </x:c>
+      <x:c r="B12" s="216" t="str">
+        <x:v>담당 범위 보존</x:v>
+      </x:c>
+      <x:c r="C12" s="216" t="str">
+        <x:v>MVC 표의 사용자/설정/마이페이지(6번), 일반 문제/오답(3번), 커뮤니티(5번) 담당자 칸을 원문 그대로 보존했다.</x:v>
+      </x:c>
+      <x:c r="D12" s="216" t="str">
+        <x:v>개발명세서(mvc), 최신화_2026-07-24</x:v>
+      </x:c>
+      <x:c r="E12" s="216" t="str">
+        <x:v>2026-07-24 로컬 문서 반영</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/최종 문서/e-학습터 개발 명세서.xlsx
+++ b/docs/최종 문서/e-학습터 개발 명세서.xlsx
@@ -2,24 +2,24 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="R5027dae005aa4c26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="Rd0d6e5788ad0424f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="R610452e39a994d6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="R9002ccadc029482c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="R6eaf143bc5d54dee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="Ra8391a7cf34e4afb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="R22924fe5c89b4ac6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="Rd50aadaa1db748e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-12" sheetId="9" r:id="R6e4481bd12f3438c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-14" sheetId="10" r:id="Rb73e088bb45a45c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-15" sheetId="11" r:id="R4d58c3c9e6854a6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-16" sheetId="12" r:id="R9893cd6c14724fa3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-19" sheetId="13" r:id="R2b8120336f4d4971"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-20" sheetId="14" r:id="R6b86f2efe5d444ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-21" sheetId="16" r:id="R07219eef8d7e4948"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-22" sheetId="17" r:id="R1cb345a6c3944f34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-23" sheetId="18" r:id="R504a583853114a33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-24" sheetId="19" r:id="Rca632e8c20b64561"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(mvc)" sheetId="1" r:id="R1983bf345d8a41a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발명세서(API)" sheetId="2" r:id="R596d61d581884ee8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추가컬럼제안" sheetId="3" r:id="R8f0008ff0589481e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-05" sheetId="4" r:id="R5d9b946e597d4ace"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-06" sheetId="5" r:id="R5bb87838512141ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-07" sheetId="6" r:id="Rc07be7c9901b4701"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-09" sheetId="7" r:id="R964ba9fafdfa4fd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-11" sheetId="8" r:id="Rc3d5ba872984480a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-12" sheetId="9" r:id="Rf1fc3839d82746bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-14" sheetId="10" r:id="R71f31b1a7b8d4fcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-15" sheetId="11" r:id="Rffcf8ffc5f5343fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-16" sheetId="12" r:id="R720a53c1794e4cda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-19" sheetId="13" r:id="R6df482046d8d4de2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-20" sheetId="14" r:id="R460525ad9c394e98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-21" sheetId="16" r:id="Rc08c38a230074fa5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-22" sheetId="17" r:id="R6005b64537da4c55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-23" sheetId="18" r:id="R64091ddf8ddb47a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최신화_2026-07-24" sheetId="19" r:id="R01d2217a99b04c55"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6772,7 +6772,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e728d3f0cee42f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd98dde6f1954034"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7215,7 +7215,7 @@
     </x:row>
     <x:row r="2" ht="40" customHeight="1">
       <x:c r="A2" s="175" t="str">
-        <x:v>기준: 2026-07-24 local source. 출석 도장과 오답노트 다운로드·커뮤니티 초안 기능을 반영했다. 요구사항·SRS·DB schema·ERD 변경 없음.</x:v>
+        <x:v>기준: 2026-07-24 local source 2c5101c·14046e9·5465a94·3f620ba·2542563·2bd2074·99bead3·0e3e9dd. SRS v1.3 → DB v2.6 → REST v2.9(변경 없음) → MVC v3.1 → 화면 설계 v2.7 → 매핑표 v0.24 → 배포 v1.3. DB schema·DDL table 정의·ERD 변경 없음.</x:v>
       </x:c>
       <x:c r="B2" s="175"/>
       <x:c r="C2" s="175"/>
@@ -7390,6 +7390,74 @@
       </x:c>
       <x:c r="E12" s="216" t="str">
         <x:v>2026-07-24 로컬 문서 반영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="88" customHeight="1">
+      <x:c r="A13" s="43" t="str">
+        <x:v>학습 진행 표시</x:v>
+      </x:c>
+      <x:c r="B13" s="43" t="str">
+        <x:v>unlock 우선 현재 레벨·진행률</x:v>
+      </x:c>
+      <x:c r="C13" s="43" t="str">
+        <x:v>선택 과목의 user_level_unlocks를 우선하고 unlock이 없을 때만 profile 값을 fallback으로 사용한다. 학습 대시보드 요약과 마이페이지는 상세 화면과 같은 분모로 계산한다.</x:v>
+      </x:c>
+      <x:c r="D13" s="43" t="str">
+        <x:v>Learning/MyPage view model, progress tests</x:v>
+      </x:c>
+      <x:c r="E13" s="43" t="str">
+        <x:v>user_level_unlocks·user_learning_profiles read / schema 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="88" customHeight="1">
+      <x:c r="A14" s="43" t="str">
+        <x:v>이론·일반 문제 UI</x:v>
+      </x:c>
+      <x:c r="B14" s="43" t="str">
+        <x:v>Markdown·유형·반응형 표시</x:v>
+      </x:c>
+      <x:c r="C14" s="43" t="str">
+        <x:v>기존 Markdown 본문을 code block·inline code·목록까지 렌더링하고 문제 유형 라벨과 lesson list/card 반응형 레이아웃을 보강한다.</x:v>
+      </x:c>
+      <x:c r="D14" s="43" t="str">
+        <x:v>lesson/practice templates, renderer CSS/JS</x:v>
+      </x:c>
+      <x:c r="E14" s="43" t="str">
+        <x:v>기존 content column 재사용 / schema 변경 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="88" customHeight="1">
+      <x:c r="A15" s="43" t="str">
+        <x:v>관리자·메일 운영</x:v>
+      </x:c>
+      <x:c r="B15" s="43" t="str">
+        <x:v>CSRF·SES 최소 로그/권한</x:v>
+      </x:c>
+      <x:c r="C15" s="43" t="str">
+        <x:v>8개 관리자 변경 form은 CSRF hidden input을 전송한다. Lambda는 SES 실패 error code만 기록하고, send 권한은 MailFrom 발신 주소 조건으로 제한한다.</x:v>
+      </x:c>
+      <x:c r="D15" s="43" t="str">
+        <x:v>admin templates, PasswordResetMailHandler, infra/aws/template.yaml, deploy.yml</x:v>
+      </x:c>
+      <x:c r="E15" s="43" t="str">
+        <x:v>public REST contract·DB schema 변경 없음 / 배포 v1.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="88" customHeight="1">
+      <x:c r="A16" s="43" t="str">
+        <x:v>문서 동기화</x:v>
+      </x:c>
+      <x:c r="B16" s="43" t="str">
+        <x:v>Notion·로컬 최종 명세</x:v>
+      </x:c>
+      <x:c r="C16" s="43" t="str">
+        <x:v>SRS v1.3, DB v2.6, MVC v3.1, 화면 설계 v2.7, 매핑표 v0.24, 추적표 v2.6, 배포 v1.3, 구현 변경 기록·7/24 일지를 같은 target-date 근거로 반영한다.</x:v>
+      </x:c>
+      <x:c r="D16" s="43" t="str">
+        <x:v>Notion direct fetch, local git log/source diff</x:v>
+      </x:c>
+      <x:c r="E16" s="43" t="str">
+        <x:v>작성자·기존 담당 범위·기존 표 구조 유지</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
